--- a/cadifa_completo_anterior.xlsx
+++ b/cadifa_completo_anterior.xlsx
@@ -454,10 +454,8 @@
           <t>citarabina</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>25351412746202499</t>
-        </is>
+      <c r="C2" t="n">
+        <v>2.53514127462025e+16</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -481,10 +479,8 @@
           <t>bilastina</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>25351030814202314</t>
-        </is>
+      <c r="C3" t="n">
+        <v>2.535103081420231e+16</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -508,10 +504,8 @@
           <t>dicloridrato de trimetazidina</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>25351281545202271</t>
-        </is>
+      <c r="C4" t="n">
+        <v>2.535128154520227e+16</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -535,10 +529,8 @@
           <t>cloridrato de venlafaxina</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>25351259212202347</t>
-        </is>
+      <c r="C5" t="n">
+        <v>2.535125921220235e+16</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -562,10 +554,8 @@
           <t>cloridrato de nafazolina</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>25351639049202301</t>
-        </is>
+      <c r="C6" t="n">
+        <v>2.53516390492023e+16</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -589,10 +579,8 @@
           <t>fumarato de tenofovir desoproxila</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>25351444404202438</t>
-        </is>
+      <c r="C7" t="n">
+        <v>2.535144440420244e+16</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -616,10 +604,8 @@
           <t>fumarato de formoterol di-hidratado</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>25351478409202201</t>
-        </is>
+      <c r="C8" t="n">
+        <v>2.53514784092022e+16</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -643,10 +629,8 @@
           <t>dapagliflozina propanodiol monoidratado</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>25351118543202417</t>
-        </is>
+      <c r="C9" t="n">
+        <v>2.535111854320242e+16</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -670,10 +654,8 @@
           <t>atogepanto hidratado</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>25351423937202303</t>
-        </is>
+      <c r="C10" t="n">
+        <v>2.53514239372023e+16</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -697,10 +679,8 @@
           <t>cloreto de suxametônio di-hidratado</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>25351661066202235</t>
-        </is>
+      <c r="C11" t="n">
+        <v>2.535166106620224e+16</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -724,10 +704,8 @@
           <t>fulvestranto</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>25351459466202282</t>
-        </is>
+      <c r="C12" t="n">
+        <v>2.535145946620228e+16</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -751,10 +729,8 @@
           <t>cloridrato de naratriptana</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>25351311863202436</t>
-        </is>
+      <c r="C13" t="n">
+        <v>2.535131186320244e+16</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -778,10 +754,8 @@
           <t>cefdinir</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>25351221963202552</t>
-        </is>
+      <c r="C14" t="n">
+        <v>2.535122196320255e+16</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -805,10 +779,8 @@
           <t>fosfato dissódico de betametasona</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>25351080720202558</t>
-        </is>
+      <c r="C15" t="n">
+        <v>2.535108072020256e+16</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -832,10 +804,8 @@
           <t>dicloridrato de betaistina</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>25351429908202428</t>
-        </is>
+      <c r="C16" t="n">
+        <v>2.535142990820243e+16</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -859,10 +829,8 @@
           <t>clortalidona</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>25351395611202451</t>
-        </is>
+      <c r="C17" t="n">
+        <v>2.535139561120245e+16</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -886,10 +854,8 @@
           <t>cloreto de suxametônio di-hidratado</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>25351238551202551</t>
-        </is>
+      <c r="C18" t="n">
+        <v>2.535123855120255e+16</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -913,10 +879,8 @@
           <t>amoxicilina tri-hidratada</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>25351061671202392</t>
-        </is>
+      <c r="C19" t="n">
+        <v>2.535106167120239e+16</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -940,10 +904,8 @@
           <t>fumarato de vonoprazana</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>25351026985202519</t>
-        </is>
+      <c r="C20" t="n">
+        <v>2.535102698520252e+16</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -967,10 +929,8 @@
           <t>semaglutida</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>25351712607202381</t>
-        </is>
+      <c r="C21" t="n">
+        <v>2.535171260720238e+16</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -994,10 +954,8 @@
           <t>melatonina</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>25351405348202335</t>
-        </is>
+      <c r="C22" t="n">
+        <v>2.535140534820234e+16</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1021,10 +979,8 @@
           <t>bilastina</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>25351373233202455</t>
-        </is>
+      <c r="C23" t="n">
+        <v>2.535137323320246e+16</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1048,10 +1004,8 @@
           <t>empagliflozina</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>25351922156202470</t>
-        </is>
+      <c r="C24" t="n">
+        <v>2.535192215620247e+16</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1075,10 +1029,8 @@
           <t>empagliflozina</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>25351481887202371</t>
-        </is>
+      <c r="C25" t="n">
+        <v>2.535148188720237e+16</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1102,10 +1054,8 @@
           <t>tegoprazana</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>25351455748202472</t>
-        </is>
+      <c r="C26" t="n">
+        <v>2.535145574820247e+16</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1129,10 +1079,8 @@
           <t>azacitidina</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>25351293719202249</t>
-        </is>
+      <c r="C27" t="n">
+        <v>2.535129371920225e+16</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1156,10 +1104,8 @@
           <t>cabergolina</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>25351296425202350</t>
-        </is>
+      <c r="C28" t="n">
+        <v>2.535129642520235e+16</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1183,10 +1129,8 @@
           <t>apixabana</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>25351171164202366</t>
-        </is>
+      <c r="C29" t="n">
+        <v>2.535117116420237e+16</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1210,10 +1154,8 @@
           <t>bilastina</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>25351082071202368</t>
-        </is>
+      <c r="C30" t="n">
+        <v>2.535108207120237e+16</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1237,10 +1179,8 @@
           <t>empagliflozina</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>25351452398202310</t>
-        </is>
+      <c r="C31" t="n">
+        <v>2.535145239820231e+16</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1264,10 +1204,8 @@
           <t>citrato de tofacitinibe</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>25351812829202301</t>
-        </is>
+      <c r="C32" t="n">
+        <v>2.53518128292023e+16</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1291,10 +1229,8 @@
           <t>clonixinato de lisina</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>25351377525202467</t>
-        </is>
+      <c r="C33" t="n">
+        <v>2.535137752520247e+16</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1318,10 +1254,8 @@
           <t>betametasona</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>25351255134202310</t>
-        </is>
+      <c r="C34" t="n">
+        <v>2.535125513420231e+16</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1345,10 +1279,8 @@
           <t>dicloridrato de trimetazidina</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>25351145158202272</t>
-        </is>
+      <c r="C35" t="n">
+        <v>2.535114515820227e+16</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1372,10 +1304,8 @@
           <t>cloridrato de givinostate monoidratado</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>25351114858202568</t>
-        </is>
+      <c r="C36" t="n">
+        <v>2.535111485820257e+16</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1399,10 +1329,8 @@
           <t>atorvastatina cálcica tri-hidratada</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>25351083726202315</t>
-        </is>
+      <c r="C37" t="n">
+        <v>2.535108372620232e+16</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1426,10 +1354,8 @@
           <t>sacubitril valsartana sódica hidratada</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>25351111892202581</t>
-        </is>
+      <c r="C38" t="n">
+        <v>2.535111189220258e+16</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -1453,10 +1379,8 @@
           <t>hidroclorotiazida</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>25351229152202508</t>
-        </is>
+      <c r="C39" t="n">
+        <v>2.535122915220251e+16</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -1480,10 +1404,8 @@
           <t>empagliflozina</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>25351068869202569</t>
-        </is>
+      <c r="C40" t="n">
+        <v>2.535106886920257e+16</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -1507,10 +1429,8 @@
           <t>nerandomilaste</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>25351059879202511</t>
-        </is>
+      <c r="C41" t="n">
+        <v>2.535105987920251e+16</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -1534,10 +1454,8 @@
           <t>hemietanolato de tucatinibe</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>25351042238202510</t>
-        </is>
+      <c r="C42" t="n">
+        <v>2.535104223820251e+16</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -1561,10 +1479,8 @@
           <t>amissulprida</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>25351058955202563</t>
-        </is>
+      <c r="C43" t="n">
+        <v>2.535105895520256e+16</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -1588,10 +1504,8 @@
           <t>cloridrato de fingolimode</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>25351061670202348</t>
-        </is>
+      <c r="C44" t="n">
+        <v>2.535106167020235e+16</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -1615,10 +1529,8 @@
           <t>pirtobrutinibe</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>25351300927202210</t>
-        </is>
+      <c r="C45" t="n">
+        <v>2.535130092720221e+16</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -1642,10 +1554,8 @@
           <t>lenalidomida</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>25351339711202317</t>
-        </is>
+      <c r="C46" t="n">
+        <v>2.535133971120232e+16</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -1669,10 +1579,8 @@
           <t>etrasimode arginina</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>25351130299202452</t>
-        </is>
+      <c r="C47" t="n">
+        <v>2.535113029920245e+16</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -1696,10 +1604,8 @@
           <t>paracetamol</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>25351028520202594</t>
-        </is>
+      <c r="C48" t="n">
+        <v>2.535102852020259e+16</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -1723,10 +1629,8 @@
           <t>esilato de nintedanibe hemi-hidratado</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>25351600438202257</t>
-        </is>
+      <c r="C49" t="n">
+        <v>2.535160043820226e+16</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -1750,10 +1654,8 @@
           <t>paracetamol</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>25351382999202340</t>
-        </is>
+      <c r="C50" t="n">
+        <v>2.535138299920234e+16</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -1777,10 +1679,8 @@
           <t>empagliflozina</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>25351410790202464</t>
-        </is>
+      <c r="C51" t="n">
+        <v>2.535141079020246e+16</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -1804,10 +1704,8 @@
           <t>milrinona</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>25351376152202245</t>
-        </is>
+      <c r="C52" t="n">
+        <v>2.535137615220224e+16</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -1831,10 +1729,8 @@
           <t>empagliflozina</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>25351604914202390</t>
-        </is>
+      <c r="C53" t="n">
+        <v>2.535160491420239e+16</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -1858,10 +1754,8 @@
           <t>empagliflozina</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>25351405815202416</t>
-        </is>
+      <c r="C54" t="n">
+        <v>2.535140581520242e+16</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -1885,10 +1779,8 @@
           <t>cloridrato de lurasidona</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>25351155278202440</t>
-        </is>
+      <c r="C55" t="n">
+        <v>2.535115527820244e+16</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -1912,10 +1804,8 @@
           <t>cloridrato do ácido aminolevulínico</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>25351152928202586</t>
-        </is>
+      <c r="C56" t="n">
+        <v>2.535115292820258e+16</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -1939,10 +1829,8 @@
           <t>palopegteriparatida</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>25351084968202598</t>
-        </is>
+      <c r="C57" t="n">
+        <v>2.53510849682026e+16</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -1966,10 +1854,8 @@
           <t>cloridrato de moxifloxacino</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>25351471785202266</t>
-        </is>
+      <c r="C58" t="n">
+        <v>2.535147178520226e+16</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -1993,10 +1879,8 @@
           <t>risperidona</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>25351042141202515</t>
-        </is>
+      <c r="C59" t="n">
+        <v>2.535104214120252e+16</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -2020,10 +1904,8 @@
           <t>cloridrato de ponatinibe</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>25351098472202500</t>
-        </is>
+      <c r="C60" t="n">
+        <v>2.53510984722025e+16</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -2047,10 +1929,8 @@
           <t>cloridrato de atomoxetina</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>25351133559202522</t>
-        </is>
+      <c r="C61" t="n">
+        <v>2.535113355920252e+16</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -2074,10 +1954,8 @@
           <t>levetiracetam</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>25351133964202460</t>
-        </is>
+      <c r="C62" t="n">
+        <v>2.535113396420246e+16</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -2101,10 +1979,8 @@
           <t>cloridrato de moxifloxacino monoidratado</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>25351004351202688</t>
-        </is>
+      <c r="C63" t="n">
+        <v>2.535100435120269e+16</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -2128,10 +2004,8 @@
           <t>ibrutinibe</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>25351193011202531</t>
-        </is>
+      <c r="C64" t="n">
+        <v>2.535119301120253e+16</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -2155,10 +2029,8 @@
           <t>dipropionato de betametasona</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>25351427731202425</t>
-        </is>
+      <c r="C65" t="n">
+        <v>2.535142773120242e+16</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -2182,10 +2054,8 @@
           <t>savolitinibe</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>25351453474202487</t>
-        </is>
+      <c r="C66" t="n">
+        <v>2.535145347420249e+16</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -2209,10 +2079,8 @@
           <t>dasatinibe monoidratado</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>25351747423202332</t>
-        </is>
+      <c r="C67" t="n">
+        <v>2.535174742320233e+16</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -2236,10 +2104,8 @@
           <t>ciclofosfamida monoidratada</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>25351705835202303</t>
-        </is>
+      <c r="C68" t="n">
+        <v>2.53517058352023e+16</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -2263,10 +2129,8 @@
           <t>cefalexina monoidratada</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>25351337677202346</t>
-        </is>
+      <c r="C69" t="n">
+        <v>2.535133767720234e+16</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -2290,10 +2154,8 @@
           <t>valsartana</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>25351098932202591</t>
-        </is>
+      <c r="C70" t="n">
+        <v>2.535109893220259e+16</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -2317,10 +2179,8 @@
           <t>clortalidona</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>25351082039202382</t>
-        </is>
+      <c r="C71" t="n">
+        <v>2.535108203920238e+16</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -2344,10 +2204,8 @@
           <t>cloridrato de pseudoefedrina</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>25351024972202505</t>
-        </is>
+      <c r="C72" t="n">
+        <v>2.53510249722025e+16</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -2371,10 +2229,8 @@
           <t>dapagliflozina propanodiol monoidratado</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>25351637166202321</t>
-        </is>
+      <c r="C73" t="n">
+        <v>2.535163716620232e+16</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -2398,10 +2254,8 @@
           <t>apixabana</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>25351507004202360</t>
-        </is>
+      <c r="C74" t="n">
+        <v>2.535150700420236e+16</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -2425,10 +2279,8 @@
           <t>regorafenibe monoidratado</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>25351161162202369</t>
-        </is>
+      <c r="C75" t="n">
+        <v>2.535116116220237e+16</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -2452,10 +2304,8 @@
           <t>pirfenidona</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>25351603004202217</t>
-        </is>
+      <c r="C76" t="n">
+        <v>2.535160300420222e+16</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -2479,10 +2329,8 @@
           <t>trometamol cetorolaco</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>25351576424202396</t>
-        </is>
+      <c r="C77" t="n">
+        <v>2.53515764242024e+16</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -2506,10 +2354,8 @@
           <t>bromidrato de vortioxetina</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>25351296191202421</t>
-        </is>
+      <c r="C78" t="n">
+        <v>2.535129619120242e+16</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -2533,10 +2379,8 @@
           <t>dipropionato de beclometasona</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>25351854627202329</t>
-        </is>
+      <c r="C79" t="n">
+        <v>2.535185462720233e+16</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -2560,10 +2404,8 @@
           <t>semaglutida</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>25351120325202515</t>
-        </is>
+      <c r="C80" t="n">
+        <v>2.535112032520252e+16</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -2587,10 +2429,8 @@
           <t>cloridrato de daunorrubicina</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>25351382977202461</t>
-        </is>
+      <c r="C81" t="n">
+        <v>2.535138297720246e+16</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -2614,10 +2454,8 @@
           <t>ácido acetilsalicílico</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>25351507003202315</t>
-        </is>
+      <c r="C82" t="n">
+        <v>2.535150700320232e+16</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -2641,10 +2479,8 @@
           <t>brivaracetam</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>25351109966202519</t>
-        </is>
+      <c r="C83" t="n">
+        <v>2.535110996620252e+16</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -2668,10 +2504,8 @@
           <t>lamivudina</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>25351041812202512</t>
-        </is>
+      <c r="C84" t="n">
+        <v>2.535104181220251e+16</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -2695,10 +2529,8 @@
           <t>melatonina</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>25351449267202347</t>
-        </is>
+      <c r="C85" t="n">
+        <v>2.535144926720235e+16</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -2722,10 +2554,8 @@
           <t>tosilato de inlunestranto</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>25351435664202412</t>
-        </is>
+      <c r="C86" t="n">
+        <v>2.535143566420241e+16</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -2749,10 +2579,8 @@
           <t>empagliflozina</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>25351127180202311</t>
-        </is>
+      <c r="C87" t="n">
+        <v>2.535112718020231e+16</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -2776,10 +2604,8 @@
           <t>fosfato de sitagliptina</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>25351581967202325</t>
-        </is>
+      <c r="C88" t="n">
+        <v>2.535158196720232e+16</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -2803,10 +2629,8 @@
           <t>dicloridrato de betaistina</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>25351403178202273</t>
-        </is>
+      <c r="C89" t="n">
+        <v>2.535140317820227e+16</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -2830,10 +2654,8 @@
           <t>empagliflozina</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>25351170349202353</t>
-        </is>
+      <c r="C90" t="n">
+        <v>2.535117034920235e+16</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -2857,10 +2679,8 @@
           <t>efavirenz</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>25351048961202421</t>
-        </is>
+      <c r="C91" t="n">
+        <v>2.535104896120242e+16</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -2884,10 +2704,8 @@
           <t>maleato de carbinoxamina</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>25351051848202261</t>
-        </is>
+      <c r="C92" t="n">
+        <v>2.535105184820226e+16</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -2911,10 +2729,8 @@
           <t>fulvestranto</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>25351648727202237</t>
-        </is>
+      <c r="C93" t="n">
+        <v>2.535164872720224e+16</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -2938,10 +2754,8 @@
           <t>linagliptina</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>25351170030202328</t>
-        </is>
+      <c r="C94" t="n">
+        <v>2.535117003020233e+16</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -2965,10 +2779,8 @@
           <t>loxoprofeno sódico di-hidratado</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>25351215604202485</t>
-        </is>
+      <c r="C95" t="n">
+        <v>2.535121560420248e+16</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -2992,10 +2804,8 @@
           <t>cloridrato de pazopanibe</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>25351605244202329</t>
-        </is>
+      <c r="C96" t="n">
+        <v>2.535160524420233e+16</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -3019,10 +2829,8 @@
           <t>dolutegravir sódico</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>25351518012202331</t>
-        </is>
+      <c r="C97" t="n">
+        <v>2.535151801220233e+16</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -3046,10 +2854,8 @@
           <t>camizestranto</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>25351081649202521</t>
-        </is>
+      <c r="C98" t="n">
+        <v>2.535108164920252e+16</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -3073,10 +2879,8 @@
           <t>rosuvastatina cálcica</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>25351416960202414</t>
-        </is>
+      <c r="C99" t="n">
+        <v>2.535141696020242e+16</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -3100,10 +2904,8 @@
           <t>micofenolato de mofetila</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>25351855315202171</t>
-        </is>
+      <c r="C100" t="n">
+        <v>2.535185531520217e+16</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -3127,10 +2929,8 @@
           <t>fostamatinibe dissódico hexaidratado</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>25351746083202322</t>
-        </is>
+      <c r="C101" t="n">
+        <v>2.535174608320232e+16</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -3154,10 +2954,8 @@
           <t>foscarbidopa hidratada</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>25351296040202210</t>
-        </is>
+      <c r="C102" t="n">
+        <v>2.535129604020221e+16</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -3181,10 +2979,8 @@
           <t>lenalidomida</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>25351484757202390</t>
-        </is>
+      <c r="C103" t="n">
+        <v>2.535148475720239e+16</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -3208,10 +3004,8 @@
           <t>carbidopa monoidratada</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>25351070479202559</t>
-        </is>
+      <c r="C104" t="n">
+        <v>2.535107047920256e+16</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -3235,10 +3029,8 @@
           <t>empagliflozina</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>25351003836202310</t>
-        </is>
+      <c r="C105" t="n">
+        <v>2.535100383620231e+16</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -3262,10 +3054,8 @@
           <t>acetato de abiraterona</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>25351364927202311</t>
-        </is>
+      <c r="C106" t="n">
+        <v>2.535136492720231e+16</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -3289,10 +3079,8 @@
           <t>pantoprazol sódico sesqui-hidratado</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>25351386918202208</t>
-        </is>
+      <c r="C107" t="n">
+        <v>2.535138691820221e+16</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -3316,10 +3104,8 @@
           <t>ácido azelaico</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>25351355934202411</t>
-        </is>
+      <c r="C108" t="n">
+        <v>2.535135593420241e+16</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -3343,10 +3129,8 @@
           <t>cloridrato de donepezila monoidratado</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>25351632628202233</t>
-        </is>
+      <c r="C109" t="n">
+        <v>2.535163262820223e+16</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -3370,10 +3154,8 @@
           <t>empagliflozina</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>25351417649202492</t>
-        </is>
+      <c r="C110" t="n">
+        <v>2.535141764920249e+16</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -3397,10 +3179,8 @@
           <t>foslevodopa</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>25351037467202512</t>
-        </is>
+      <c r="C111" t="n">
+        <v>2.535103746720251e+16</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -3424,10 +3204,8 @@
           <t>maleato de timolol</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>25351659911202211</t>
-        </is>
+      <c r="C112" t="n">
+        <v>2.535165991120221e+16</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -3451,10 +3229,8 @@
           <t>fumarato de tenofovir desoproxila</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>25351380515202417</t>
-        </is>
+      <c r="C113" t="n">
+        <v>2.535138051520242e+16</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -3478,10 +3254,8 @@
           <t>dapagliflozina propanodiol monoidratado</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>25351146725202216</t>
-        </is>
+      <c r="C114" t="n">
+        <v>2.535114672520222e+16</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -3505,10 +3279,8 @@
           <t>clortalidona</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>25351223025202325</t>
-        </is>
+      <c r="C115" t="n">
+        <v>2.535122302520232e+16</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -3532,10 +3304,8 @@
           <t>ezetimiba</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>25351130792202219</t>
-        </is>
+      <c r="C116" t="n">
+        <v>2.535113079220222e+16</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -3559,10 +3329,8 @@
           <t>fezolinetanto</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>25351574648202282</t>
-        </is>
+      <c r="C117" t="n">
+        <v>2.535157464820228e+16</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -3586,10 +3354,8 @@
           <t>apixabana</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>25351466090202262</t>
-        </is>
+      <c r="C118" t="n">
+        <v>2.535146609020226e+16</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -3613,10 +3379,8 @@
           <t>fezolinetanto</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>25351574663202221</t>
-        </is>
+      <c r="C119" t="n">
+        <v>2.535157466320222e+16</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -3640,10 +3404,8 @@
           <t>etodolaco</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>25351071656202271</t>
-        </is>
+      <c r="C120" t="n">
+        <v>2.535107165620227e+16</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -3667,10 +3429,8 @@
           <t>acetato de abiraterona</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>25351513882202152</t>
-        </is>
+      <c r="C121" t="n">
+        <v>2.535151388220215e+16</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -3694,10 +3454,8 @@
           <t>clavulanato de potássio</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>25351450251202468</t>
-        </is>
+      <c r="C122" t="n">
+        <v>2.535145025120247e+16</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -3721,10 +3479,8 @@
           <t>tirzepatida</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>25351043565202416</t>
-        </is>
+      <c r="C123" t="n">
+        <v>2.535104356520242e+16</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -3748,10 +3504,8 @@
           <t>travoprosta</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>25351657311202218</t>
-        </is>
+      <c r="C124" t="n">
+        <v>2.535165731120222e+16</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -3775,10 +3529,8 @@
           <t>eltrombopague olamina</t>
         </is>
       </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>25351558333202379</t>
-        </is>
+      <c r="C125" t="n">
+        <v>2.535155833320238e+16</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -3802,10 +3554,8 @@
           <t>miltefosina</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>25351438894202433</t>
-        </is>
+      <c r="C126" t="n">
+        <v>2.535143889420243e+16</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -3829,10 +3579,8 @@
           <t>cloridrato de metformina</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>25351586381202276</t>
-        </is>
+      <c r="C127" t="n">
+        <v>2.535158638120228e+16</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -3856,10 +3604,8 @@
           <t>cloridrato de fenilefrina</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>25351409236202272</t>
-        </is>
+      <c r="C128" t="n">
+        <v>2.535140923620227e+16</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -3883,10 +3629,8 @@
           <t>vildagliptina</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>25351204151202208</t>
-        </is>
+      <c r="C129" t="n">
+        <v>2.535120415120221e+16</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -3910,10 +3654,8 @@
           <t>lamivudina</t>
         </is>
       </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>25351375823202412</t>
-        </is>
+      <c r="C130" t="n">
+        <v>2.535137582320241e+16</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -3937,10 +3679,8 @@
           <t>dolutegravir sódico hidratado</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>25351451401202451</t>
-        </is>
+      <c r="C131" t="n">
+        <v>2.535145140120245e+16</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -3964,10 +3704,8 @@
           <t>cloridrato de clomipramina</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>25351121192202413</t>
-        </is>
+      <c r="C132" t="n">
+        <v>2.535112119220241e+16</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -3991,10 +3729,8 @@
           <t>gliclazida</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>25351779850202380</t>
-        </is>
+      <c r="C133" t="n">
+        <v>2.535177985020238e+16</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -4018,10 +3754,8 @@
           <t>acetato de noretisterona</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>25351399291202417</t>
-        </is>
+      <c r="C134" t="n">
+        <v>2.535139929120242e+16</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -4045,10 +3779,8 @@
           <t>mesalazina</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>25351101861202279</t>
-        </is>
+      <c r="C135" t="n">
+        <v>2.535110186120228e+16</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -4072,10 +3804,8 @@
           <t>cloridrato de ivabradina</t>
         </is>
       </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>25351071292202572</t>
-        </is>
+      <c r="C136" t="n">
+        <v>2.535107129220257e+16</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -4099,10 +3829,8 @@
           <t>dapagliflozina</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>25351434552202363</t>
-        </is>
+      <c r="C137" t="n">
+        <v>2.535143455220236e+16</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -4126,10 +3854,8 @@
           <t>dapagliflozina</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>25351601377202326</t>
-        </is>
+      <c r="C138" t="n">
+        <v>2.535160137720233e+16</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -4153,10 +3879,8 @@
           <t>levetiracetam</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>25351294094202232</t>
-        </is>
+      <c r="C139" t="n">
+        <v>2.535129409420223e+16</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -4180,10 +3904,8 @@
           <t>vildagliptina</t>
         </is>
       </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>25351244351202295</t>
-        </is>
+      <c r="C140" t="n">
+        <v>2.53512443512023e+16</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -4207,10 +3929,8 @@
           <t>cenobamato</t>
         </is>
       </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>25351210705202460</t>
-        </is>
+      <c r="C141" t="n">
+        <v>2.535121070520246e+16</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -4234,10 +3954,8 @@
           <t>anastrozol</t>
         </is>
       </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>25351246621202201</t>
-        </is>
+      <c r="C142" t="n">
+        <v>2.53512466212022e+16</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -4261,10 +3979,8 @@
           <t>topiramato</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>25351380504202429</t>
-        </is>
+      <c r="C143" t="n">
+        <v>2.535138050420243e+16</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -4288,10 +4004,8 @@
           <t>montelucaste de sódio</t>
         </is>
       </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>25351482067202215</t>
-        </is>
+      <c r="C144" t="n">
+        <v>2.535148206720222e+16</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -4315,10 +4029,8 @@
           <t>tosilato de edoxabana monoidratado</t>
         </is>
       </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>25351148227202461</t>
-        </is>
+      <c r="C145" t="n">
+        <v>2.535114822720246e+16</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -4342,10 +4054,8 @@
           <t>sirolimo</t>
         </is>
       </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>25351888384202411</t>
-        </is>
+      <c r="C146" t="n">
+        <v>2.535188838420241e+16</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -4369,10 +4079,8 @@
           <t>furoato de mometasona monoidratado</t>
         </is>
       </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>25351376523202451</t>
-        </is>
+      <c r="C147" t="n">
+        <v>2.535137652320245e+16</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -4396,10 +4104,8 @@
           <t>fumarato de tenofovir desoproxila</t>
         </is>
       </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>25351013614202569</t>
-        </is>
+      <c r="C148" t="n">
+        <v>2.535101361420257e+16</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -4423,10 +4129,8 @@
           <t>fenilefrina</t>
         </is>
       </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>25351096355202331</t>
-        </is>
+      <c r="C149" t="n">
+        <v>2.535109635520233e+16</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -4450,10 +4154,8 @@
           <t>bimatoprosta</t>
         </is>
       </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>25351364595202374</t>
-        </is>
+      <c r="C150" t="n">
+        <v>2.535136459520238e+16</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -4477,10 +4179,8 @@
           <t>levomalato de cabozantinibe</t>
         </is>
       </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>25351324307202420</t>
-        </is>
+      <c r="C151" t="n">
+        <v>2.535132430720242e+16</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -4504,10 +4204,8 @@
           <t>cloridrato de trazodona</t>
         </is>
       </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>25351177610202346</t>
-        </is>
+      <c r="C152" t="n">
+        <v>2.535117761020234e+16</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -4531,10 +4229,8 @@
           <t>succinato de metoprolol</t>
         </is>
       </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>25351564144202254</t>
-        </is>
+      <c r="C153" t="n">
+        <v>2.535156414420226e+16</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -4558,10 +4254,8 @@
           <t>paclitaxel</t>
         </is>
       </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>25351348787202252</t>
-        </is>
+      <c r="C154" t="n">
+        <v>2.535134878720225e+16</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -4585,10 +4279,8 @@
           <t>cloridrato  de ondansetrona di-hidratado</t>
         </is>
       </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>25351314351202341</t>
-        </is>
+      <c r="C155" t="n">
+        <v>2.535131435120234e+16</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -4612,10 +4304,8 @@
           <t>fitusirana sódica</t>
         </is>
       </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>25351805707202351</t>
-        </is>
+      <c r="C156" t="n">
+        <v>2.535180570720235e+16</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -4639,10 +4329,8 @@
           <t>entricitabina</t>
         </is>
       </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>25351449294202409</t>
-        </is>
+      <c r="C157" t="n">
+        <v>2.535144929420241e+16</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -4666,10 +4354,8 @@
           <t>calcipotriol monoidratado</t>
         </is>
       </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>25351000683202511</t>
-        </is>
+      <c r="C158" t="n">
+        <v>2.535100068320251e+16</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -4693,10 +4379,8 @@
           <t>vildagliptina</t>
         </is>
       </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>25351020952202395</t>
-        </is>
+      <c r="C159" t="n">
+        <v>2.53510209522024e+16</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -4720,10 +4404,8 @@
           <t>eltrombopague olamina</t>
         </is>
       </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>25351106130202481</t>
-        </is>
+      <c r="C160" t="n">
+        <v>2.535110613020248e+16</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -4747,10 +4429,8 @@
           <t>mirabegrona</t>
         </is>
       </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>25351404684202280</t>
-        </is>
+      <c r="C161" t="n">
+        <v>2.535140468420228e+16</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -4774,10 +4454,8 @@
           <t>avacincaptade pegol sódico</t>
         </is>
       </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>25351046702202547</t>
-        </is>
+      <c r="C162" t="n">
+        <v>2.535104670220255e+16</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -4801,10 +4479,8 @@
           <t>latanoprosta</t>
         </is>
       </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>25351618787202225</t>
-        </is>
+      <c r="C163" t="n">
+        <v>2.535161878720222e+16</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -4828,10 +4504,8 @@
           <t>citrato de pacritinibe</t>
         </is>
       </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>25351424448202441</t>
-        </is>
+      <c r="C164" t="n">
+        <v>2.535142444820244e+16</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -4855,10 +4529,8 @@
           <t>losartana potássica</t>
         </is>
       </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>25351577562202210</t>
-        </is>
+      <c r="C165" t="n">
+        <v>2.535157756220221e+16</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -4882,10 +4554,8 @@
           <t>sulfato de bleomicina</t>
         </is>
       </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>25351126520202478</t>
-        </is>
+      <c r="C166" t="n">
+        <v>2.535112652020248e+16</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -4909,10 +4579,8 @@
           <t>leflunomida</t>
         </is>
       </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>25351595107202298</t>
-        </is>
+      <c r="C167" t="n">
+        <v>2.53515951072023e+16</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -4936,10 +4604,8 @@
           <t>fruquintinibe</t>
         </is>
       </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>25351062240202513</t>
-        </is>
+      <c r="C168" t="n">
+        <v>2.535106224020251e+16</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -4963,10 +4629,8 @@
           <t>arpraziquantel</t>
         </is>
       </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>25351264640202472</t>
-        </is>
+      <c r="C169" t="n">
+        <v>2.535126464020247e+16</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -4990,10 +4654,8 @@
           <t>palbociclibe</t>
         </is>
       </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>25351602992202279</t>
-        </is>
+      <c r="C170" t="n">
+        <v>2.535160299220228e+16</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -5017,10 +4679,8 @@
           <t>risedronato sódico hemipentaidratado</t>
         </is>
       </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>25351417879202451</t>
-        </is>
+      <c r="C171" t="n">
+        <v>2.535141787920245e+16</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -5044,10 +4704,8 @@
           <t>levodopa</t>
         </is>
       </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>25351396231202434</t>
-        </is>
+      <c r="C172" t="n">
+        <v>2.535139623120243e+16</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -5071,10 +4729,8 @@
           <t>hemifumarato de quetiapina</t>
         </is>
       </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>25351609899202295</t>
-        </is>
+      <c r="C173" t="n">
+        <v>2.53516098992023e+16</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -5098,10 +4754,8 @@
           <t>nitazoxanida</t>
         </is>
       </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>25351645270202217</t>
-        </is>
+      <c r="C174" t="n">
+        <v>2.535164527020222e+16</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -5125,10 +4779,8 @@
           <t>nitrato de fenticonazol</t>
         </is>
       </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>25351014971202544</t>
-        </is>
+      <c r="C175" t="n">
+        <v>2.535101497120254e+16</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -5152,10 +4804,8 @@
           <t>cloridrato  de ondansetrona di-hidratado</t>
         </is>
       </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>25351236293202498</t>
-        </is>
+      <c r="C176" t="n">
+        <v>2.53512362932025e+16</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -5179,10 +4829,8 @@
           <t>cloridrato de ciclobenzaprina</t>
         </is>
       </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>25351377050202417</t>
-        </is>
+      <c r="C177" t="n">
+        <v>2.535137705020242e+16</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -5206,10 +4854,8 @@
           <t>brometo de glicopirrônio</t>
         </is>
       </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>25351866447202390</t>
-        </is>
+      <c r="C178" t="n">
+        <v>2.535186644720239e+16</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -5233,10 +4879,8 @@
           <t>ezetimiba</t>
         </is>
       </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>25351011622202571</t>
-        </is>
+      <c r="C179" t="n">
+        <v>2.535101162220257e+16</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -5260,10 +4904,8 @@
           <t>peróxido de benzoíla</t>
         </is>
       </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>25351431150202498</t>
-        </is>
+      <c r="C180" t="n">
+        <v>2.53514311502025e+16</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -5287,10 +4929,8 @@
           <t>fosfato de sitagliptina</t>
         </is>
       </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>25351648234202205</t>
-        </is>
+      <c r="C181" t="n">
+        <v>2.53516482342022e+16</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -5314,10 +4954,8 @@
           <t>maleato de bronfeniramina</t>
         </is>
       </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>25351694996202356</t>
-        </is>
+      <c r="C182" t="n">
+        <v>2.535169499620236e+16</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -5341,10 +4979,8 @@
           <t>mesilato de eribulina</t>
         </is>
       </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>25351456286202419</t>
-        </is>
+      <c r="C183" t="n">
+        <v>2.535145628620242e+16</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -5368,10 +5004,8 @@
           <t>apremilaste</t>
         </is>
       </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>25351402841202484</t>
-        </is>
+      <c r="C184" t="n">
+        <v>2.535140284120248e+16</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -5395,10 +5029,8 @@
           <t>bilastina</t>
         </is>
       </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>25351035922202383</t>
-        </is>
+      <c r="C185" t="n">
+        <v>2.535103592220238e+16</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -5422,10 +5054,8 @@
           <t>fosfomicina trometamol</t>
         </is>
       </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>25351373156202433</t>
-        </is>
+      <c r="C186" t="n">
+        <v>2.535137315620243e+16</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -5449,10 +5079,8 @@
           <t>bimatoprosta</t>
         </is>
       </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>25351594980202263</t>
-        </is>
+      <c r="C187" t="n">
+        <v>2.535159498020226e+16</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -5476,10 +5104,8 @@
           <t>oxalato de escitalopram</t>
         </is>
       </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>25351501193202367</t>
-        </is>
+      <c r="C188" t="n">
+        <v>2.535150119320237e+16</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -5503,10 +5129,8 @@
           <t>dasatinibe monoidratado</t>
         </is>
       </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>25351846331202172</t>
-        </is>
+      <c r="C189" t="n">
+        <v>2.535184633120217e+16</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -5530,10 +5154,8 @@
           <t>cefazolina sódica</t>
         </is>
       </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>25351371359202495</t>
-        </is>
+      <c r="C190" t="n">
+        <v>2.53513713592025e+16</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -5557,10 +5179,8 @@
           <t>fosfato de oseltamivir</t>
         </is>
       </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>25351104144202461</t>
-        </is>
+      <c r="C191" t="n">
+        <v>2.535110414420246e+16</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -5584,10 +5204,8 @@
           <t>macitentana</t>
         </is>
       </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>25351000069202541</t>
-        </is>
+      <c r="C192" t="n">
+        <v>2.535100006920254e+16</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -5611,10 +5229,8 @@
           <t>bimatoprosta</t>
         </is>
       </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>25351440095202265</t>
-        </is>
+      <c r="C193" t="n">
+        <v>2.535144009520226e+16</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -5638,10 +5254,8 @@
           <t>cloridrato de acoramidis</t>
         </is>
       </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>25351209898202414</t>
-        </is>
+      <c r="C194" t="n">
+        <v>2.535120989820242e+16</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -5665,10 +5279,8 @@
           <t>ramelteona</t>
         </is>
       </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>25351248600202301</t>
-        </is>
+      <c r="C195" t="n">
+        <v>2.53512486002023e+16</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -5692,10 +5304,8 @@
           <t>entricitabina</t>
         </is>
       </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>25351013575202508</t>
-        </is>
+      <c r="C196" t="n">
+        <v>2.535101357520251e+16</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -5719,10 +5329,8 @@
           <t>cloridrato de olopatadina</t>
         </is>
       </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>25351456102202241</t>
-        </is>
+      <c r="C197" t="n">
+        <v>2.535145610220224e+16</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -5746,10 +5354,8 @@
           <t>sepiapterina</t>
         </is>
       </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>25351392291202488</t>
-        </is>
+      <c r="C198" t="n">
+        <v>2.535139229120249e+16</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -5773,10 +5379,8 @@
           <t>cloridrato de sertralina</t>
         </is>
       </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>25351367784202480</t>
-        </is>
+      <c r="C199" t="n">
+        <v>2.535136778420248e+16</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -5800,10 +5404,8 @@
           <t>dacarbazina</t>
         </is>
       </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>25351046241202511</t>
-        </is>
+      <c r="C200" t="n">
+        <v>2.535104624120251e+16</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -5827,10 +5429,8 @@
           <t>cloridrato de sertralina</t>
         </is>
       </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>25351372758202392</t>
-        </is>
+      <c r="C201" t="n">
+        <v>2.535137275820239e+16</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -5854,10 +5454,8 @@
           <t>cloridrato de clonidina</t>
         </is>
       </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>25351228507202291</t>
-        </is>
+      <c r="C202" t="n">
+        <v>2.535122850720229e+16</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -5881,10 +5479,8 @@
           <t>paracetamol</t>
         </is>
       </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>25351143488202223</t>
-        </is>
+      <c r="C203" t="n">
+        <v>2.535114348820222e+16</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -5908,10 +5504,8 @@
           <t>bilastina monoidratada</t>
         </is>
       </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>25351222993202233</t>
-        </is>
+      <c r="C204" t="n">
+        <v>2.535122299320223e+16</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -5935,10 +5529,8 @@
           <t>dimesilato de lisdexanfetamina</t>
         </is>
       </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>25351774003202329</t>
-        </is>
+      <c r="C205" t="n">
+        <v>2.535177400320233e+16</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -5962,10 +5554,8 @@
           <t>ácido azelaico</t>
         </is>
       </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>25351724767202373</t>
-        </is>
+      <c r="C206" t="n">
+        <v>2.535172476720237e+16</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -5989,10 +5579,8 @@
           <t>acetato de clormadinona</t>
         </is>
       </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>25351076889202422</t>
-        </is>
+      <c r="C207" t="n">
+        <v>2.535107688920242e+16</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -6016,10 +5604,8 @@
           <t>temozolomida</t>
         </is>
       </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>25351766094202329</t>
-        </is>
+      <c r="C208" t="n">
+        <v>2.535176609420233e+16</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -6043,10 +5629,8 @@
           <t>bromidrato de tazemetostate</t>
         </is>
       </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>25351424720202493</t>
-        </is>
+      <c r="C209" t="n">
+        <v>2.535142472020249e+16</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -6070,10 +5654,8 @@
           <t>acetato de terlipressina</t>
         </is>
       </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>25351009574202551</t>
-        </is>
+      <c r="C210" t="n">
+        <v>2.535100957420255e+16</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -6097,10 +5679,8 @@
           <t>lenacapavir sódico</t>
         </is>
       </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>25351419859202415</t>
-        </is>
+      <c r="C211" t="n">
+        <v>2.535141985920242e+16</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -6124,10 +5704,8 @@
           <t>cloridrato de sertralina</t>
         </is>
       </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>25351250720202360</t>
-        </is>
+      <c r="C212" t="n">
+        <v>2.535125072020236e+16</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -6151,10 +5729,8 @@
           <t>azitromicina di-hidratada</t>
         </is>
       </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>25351581742202115</t>
-        </is>
+      <c r="C213" t="n">
+        <v>2.535158174220212e+16</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -6178,10 +5754,8 @@
           <t>cloridrato de moxifloxacino</t>
         </is>
       </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>25351455707202214</t>
-        </is>
+      <c r="C214" t="n">
+        <v>2.535145570720222e+16</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -6205,10 +5779,8 @@
           <t>bromidrato de vortioxetina</t>
         </is>
       </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>25351632937202211</t>
-        </is>
+      <c r="C215" t="n">
+        <v>2.535163293720221e+16</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -6232,10 +5804,8 @@
           <t>bromidrato de dextrometorfano monoidratado</t>
         </is>
       </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>25351235325202357</t>
-        </is>
+      <c r="C216" t="n">
+        <v>2.535123532520236e+16</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -6259,10 +5829,8 @@
           <t>inavolisibe</t>
         </is>
       </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>25351359290202421</t>
-        </is>
+      <c r="C217" t="n">
+        <v>2.535135929020242e+16</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -6286,10 +5854,8 @@
           <t>oxalato de escitalopram</t>
         </is>
       </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>25351362096202181</t>
-        </is>
+      <c r="C218" t="n">
+        <v>2.535136209620218e+16</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -6313,10 +5879,8 @@
           <t>cloridrato de lurasidona</t>
         </is>
       </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>25351637498202314</t>
-        </is>
+      <c r="C219" t="n">
+        <v>2.535163749820231e+16</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -6340,10 +5904,8 @@
           <t>cloridrato de metformina</t>
         </is>
       </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>25351289158202364</t>
-        </is>
+      <c r="C220" t="n">
+        <v>2.535128915820236e+16</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -6367,10 +5929,8 @@
           <t>anastrozol</t>
         </is>
       </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>25351213099202272</t>
-        </is>
+      <c r="C221" t="n">
+        <v>2.535121309920227e+16</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -6394,10 +5954,8 @@
           <t>midostaurina</t>
         </is>
       </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>25351535884202283</t>
-        </is>
+      <c r="C222" t="n">
+        <v>2.535153588420228e+16</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -6421,10 +5979,8 @@
           <t>olaparibe</t>
         </is>
       </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>25351384266202421</t>
-        </is>
+      <c r="C223" t="n">
+        <v>2.535138426620242e+16</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -6448,10 +6004,8 @@
           <t>ezetimiba</t>
         </is>
       </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>25351376538202257</t>
-        </is>
+      <c r="C224" t="n">
+        <v>2.535137653820226e+16</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -6475,10 +6029,8 @@
           <t>cloridrato de metformina</t>
         </is>
       </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>25351290782202223</t>
-        </is>
+      <c r="C225" t="n">
+        <v>2.535129078220222e+16</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -6502,10 +6054,8 @@
           <t>cloridrato de levobupivacaína</t>
         </is>
       </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>25351430629202415</t>
-        </is>
+      <c r="C226" t="n">
+        <v>2.535143062920242e+16</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -6529,10 +6079,8 @@
           <t>cloridrato de dextrobupivacaína</t>
         </is>
       </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>25351430646202444</t>
-        </is>
+      <c r="C227" t="n">
+        <v>2.535143064620244e+16</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -6556,10 +6104,8 @@
           <t>argipressina</t>
         </is>
       </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>25351361638202441</t>
-        </is>
+      <c r="C228" t="n">
+        <v>2.535136163820244e+16</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -6583,10 +6129,8 @@
           <t>estiripentol</t>
         </is>
       </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>25351247171202427</t>
-        </is>
+      <c r="C229" t="n">
+        <v>2.535124717120243e+16</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -6610,10 +6154,8 @@
           <t>olmesartana medoxomila</t>
         </is>
       </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>25351279011202447</t>
-        </is>
+      <c r="C230" t="n">
+        <v>2.535127901120245e+16</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -6637,10 +6179,8 @@
           <t>brivaracetam</t>
         </is>
       </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>25351300253202415</t>
-        </is>
+      <c r="C231" t="n">
+        <v>2.535130025320242e+16</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -6664,10 +6204,8 @@
           <t>estiripentol</t>
         </is>
       </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>25351247172202471</t>
-        </is>
+      <c r="C232" t="n">
+        <v>2.535124717220247e+16</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -6691,10 +6229,8 @@
           <t>hemitartarato de zolpidem</t>
         </is>
       </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>25351572312202285</t>
-        </is>
+      <c r="C233" t="n">
+        <v>2.535157231220228e+16</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -6718,10 +6254,8 @@
           <t>fosfato sódico de prednisolona</t>
         </is>
       </c>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>25351417556202468</t>
-        </is>
+      <c r="C234" t="n">
+        <v>2.535141755620247e+16</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -6745,10 +6279,8 @@
           <t>fosfato dissódico de dexametasona</t>
         </is>
       </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>25351415104202361</t>
-        </is>
+      <c r="C235" t="n">
+        <v>2.535141510420236e+16</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -6772,10 +6304,8 @@
           <t>sevabertinibe</t>
         </is>
       </c>
-      <c r="C236" t="inlineStr">
-        <is>
-          <t>25351062927202541</t>
-        </is>
+      <c r="C236" t="n">
+        <v>2.535106292720254e+16</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -6799,10 +6329,8 @@
           <t>cloridrato de moxifloxacino monoidratado</t>
         </is>
       </c>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>25351379836202380</t>
-        </is>
+      <c r="C237" t="n">
+        <v>2.535137983620238e+16</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -6826,10 +6354,8 @@
           <t>lenalidomida</t>
         </is>
       </c>
-      <c r="C238" t="inlineStr">
-        <is>
-          <t>25351431432202495</t>
-        </is>
+      <c r="C238" t="n">
+        <v>2.53514314322025e+16</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -6853,10 +6379,8 @@
           <t>pregabalina</t>
         </is>
       </c>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>25351637304202291</t>
-        </is>
+      <c r="C239" t="n">
+        <v>2.535163730420229e+16</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -6880,10 +6404,8 @@
           <t>latanoprosta</t>
         </is>
       </c>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>25351577589202202</t>
-        </is>
+      <c r="C240" t="n">
+        <v>2.53515775892022e+16</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -6907,10 +6429,8 @@
           <t>adapaleno</t>
         </is>
       </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>25351439221202409</t>
-        </is>
+      <c r="C241" t="n">
+        <v>2.535143922120241e+16</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -6934,10 +6454,8 @@
           <t>fosfato de sitagliptina monoidratado</t>
         </is>
       </c>
-      <c r="C242" t="inlineStr">
-        <is>
-          <t>25351503091202203</t>
-        </is>
+      <c r="C242" t="n">
+        <v>2.53515030912022e+16</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -6961,10 +6479,8 @@
           <t>cloridrato de propranolol</t>
         </is>
       </c>
-      <c r="C243" t="inlineStr">
-        <is>
-          <t>25351356317202262</t>
-        </is>
+      <c r="C243" t="n">
+        <v>2.535135631720226e+16</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -6988,10 +6504,8 @@
           <t>tezacaftor</t>
         </is>
       </c>
-      <c r="C244" t="inlineStr">
-        <is>
-          <t>25351361874202386</t>
-        </is>
+      <c r="C244" t="n">
+        <v>2.535136187420238e+16</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -7015,10 +6529,8 @@
           <t>maleato de fluvoxamina</t>
         </is>
       </c>
-      <c r="C245" t="inlineStr">
-        <is>
-          <t>25351223864202424</t>
-        </is>
+      <c r="C245" t="n">
+        <v>2.535122386420242e+16</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -7042,10 +6554,8 @@
           <t>ibuprofeno</t>
         </is>
       </c>
-      <c r="C246" t="inlineStr">
-        <is>
-          <t>25351305688202286</t>
-        </is>
+      <c r="C246" t="n">
+        <v>2.535130568820229e+16</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -7069,10 +6579,8 @@
           <t>oxalato de escitalopram</t>
         </is>
       </c>
-      <c r="C247" t="inlineStr">
-        <is>
-          <t>25351548824202221</t>
-        </is>
+      <c r="C247" t="n">
+        <v>2.535154882420222e+16</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -7096,10 +6604,8 @@
           <t>cloridrato de bupivacaína monoidratado</t>
         </is>
       </c>
-      <c r="C248" t="inlineStr">
-        <is>
-          <t>25351413099202432</t>
-        </is>
+      <c r="C248" t="n">
+        <v>2.535141309920243e+16</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -7123,10 +6629,8 @@
           <t>cloridrato de ciclobenzaprina</t>
         </is>
       </c>
-      <c r="C249" t="inlineStr">
-        <is>
-          <t>25351234633202284</t>
-        </is>
+      <c r="C249" t="n">
+        <v>2.535123463320228e+16</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -7150,10 +6654,8 @@
           <t>orlistate</t>
         </is>
       </c>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>25351281650202391</t>
-        </is>
+      <c r="C250" t="n">
+        <v>2.535128165020239e+16</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -7177,10 +6679,8 @@
           <t>estradiol hemi-hidratado</t>
         </is>
       </c>
-      <c r="C251" t="inlineStr">
-        <is>
-          <t>25351190997202326</t>
-        </is>
+      <c r="C251" t="n">
+        <v>2.535119099720233e+16</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -7204,10 +6704,8 @@
           <t>cloridrato de fenfluramina</t>
         </is>
       </c>
-      <c r="C252" t="inlineStr">
-        <is>
-          <t>25351148701202455</t>
-        </is>
+      <c r="C252" t="n">
+        <v>2.535114870120246e+16</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -7231,10 +6729,8 @@
           <t>divalproato de sódio</t>
         </is>
       </c>
-      <c r="C253" t="inlineStr">
-        <is>
-          <t>25351627056202271</t>
-        </is>
+      <c r="C253" t="n">
+        <v>2.535162705620227e+16</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -7258,10 +6754,8 @@
           <t>hidroclorotiazida</t>
         </is>
       </c>
-      <c r="C254" t="inlineStr">
-        <is>
-          <t>25351307815202443</t>
-        </is>
+      <c r="C254" t="n">
+        <v>2.535130781520244e+16</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -7285,10 +6779,8 @@
           <t>dienogeste</t>
         </is>
       </c>
-      <c r="C255" t="inlineStr">
-        <is>
-          <t>25351512765202333</t>
-        </is>
+      <c r="C255" t="n">
+        <v>2.535151276520233e+16</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -7312,10 +6804,8 @@
           <t>mirabegrona</t>
         </is>
       </c>
-      <c r="C256" t="inlineStr">
-        <is>
-          <t>25351501765202227</t>
-        </is>
+      <c r="C256" t="n">
+        <v>2.535150176520223e+16</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -7339,10 +6829,8 @@
           <t>dexlansoprazol sesqui-hidratado</t>
         </is>
       </c>
-      <c r="C257" t="inlineStr">
-        <is>
-          <t>25351397786202401</t>
-        </is>
+      <c r="C257" t="n">
+        <v>2.53513977862024e+16</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -7366,10 +6854,8 @@
           <t>fosfato de oseltamivir</t>
         </is>
       </c>
-      <c r="C258" t="inlineStr">
-        <is>
-          <t>25351205813202411</t>
-        </is>
+      <c r="C258" t="n">
+        <v>2.535120581320241e+16</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -7393,10 +6879,8 @@
           <t>prednisolona</t>
         </is>
       </c>
-      <c r="C259" t="inlineStr">
-        <is>
-          <t>25351399589202257</t>
-        </is>
+      <c r="C259" t="n">
+        <v>2.535139958920226e+16</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -7420,10 +6904,8 @@
           <t>furoato de mometasona monoidratado</t>
         </is>
       </c>
-      <c r="C260" t="inlineStr">
-        <is>
-          <t>25351408483202413</t>
-        </is>
+      <c r="C260" t="n">
+        <v>2.535140848320241e+16</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -7447,10 +6929,8 @@
           <t>ibuprofeno</t>
         </is>
       </c>
-      <c r="C261" t="inlineStr">
-        <is>
-          <t>25351538000202242</t>
-        </is>
+      <c r="C261" t="n">
+        <v>2.535153800020224e+16</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -7474,10 +6954,8 @@
           <t>empagliflozina</t>
         </is>
       </c>
-      <c r="C262" t="inlineStr">
-        <is>
-          <t>25351208397202411</t>
-        </is>
+      <c r="C262" t="n">
+        <v>2.535120839720241e+16</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -7501,10 +6979,8 @@
           <t>dapagliflozina butanodiol monoidratado</t>
         </is>
       </c>
-      <c r="C263" t="inlineStr">
-        <is>
-          <t>25351387748202432</t>
-        </is>
+      <c r="C263" t="n">
+        <v>2.535138774820243e+16</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -7528,10 +7004,8 @@
           <t>eplontersena sódica</t>
         </is>
       </c>
-      <c r="C264" t="inlineStr">
-        <is>
-          <t>25351837528202382</t>
-        </is>
+      <c r="C264" t="n">
+        <v>2.535183752820238e+16</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -7555,10 +7029,8 @@
           <t>carvedilol</t>
         </is>
       </c>
-      <c r="C265" t="inlineStr">
-        <is>
-          <t>25351141272202312</t>
-        </is>
+      <c r="C265" t="n">
+        <v>2.535114127220231e+16</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -7582,10 +7054,8 @@
           <t>paclitaxel</t>
         </is>
       </c>
-      <c r="C266" t="inlineStr">
-        <is>
-          <t>25351383927202409</t>
-        </is>
+      <c r="C266" t="n">
+        <v>2.535138392720241e+16</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -7609,10 +7079,8 @@
           <t>bissulfato de clopidogrel</t>
         </is>
       </c>
-      <c r="C267" t="inlineStr">
-        <is>
-          <t>25351334000202275</t>
-        </is>
+      <c r="C267" t="n">
+        <v>2.535133400020228e+16</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -7636,10 +7104,8 @@
           <t>micafungina sódica</t>
         </is>
       </c>
-      <c r="C268" t="inlineStr">
-        <is>
-          <t>25351428878202351</t>
-        </is>
+      <c r="C268" t="n">
+        <v>2.535142887820235e+16</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -7663,10 +7129,8 @@
           <t>cloridrato de lurasidona</t>
         </is>
       </c>
-      <c r="C269" t="inlineStr">
-        <is>
-          <t>25351497520202379</t>
-        </is>
+      <c r="C269" t="n">
+        <v>2.535149752020238e+16</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -7690,10 +7154,8 @@
           <t>cloridrato de melfalana</t>
         </is>
       </c>
-      <c r="C270" t="inlineStr">
-        <is>
-          <t>25351161161202314</t>
-        </is>
+      <c r="C270" t="n">
+        <v>2.535116116120231e+16</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -7717,10 +7179,8 @@
           <t>olanzapina</t>
         </is>
       </c>
-      <c r="C271" t="inlineStr">
-        <is>
-          <t>25351270853202352</t>
-        </is>
+      <c r="C271" t="n">
+        <v>2.535127085320235e+16</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -7744,10 +7204,8 @@
           <t>cloridrato de fenilefrina</t>
         </is>
       </c>
-      <c r="C272" t="inlineStr">
-        <is>
-          <t>25351197305202371</t>
-        </is>
+      <c r="C272" t="n">
+        <v>2.535119730520237e+16</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -7771,10 +7229,8 @@
           <t>cloridrato de buspirona</t>
         </is>
       </c>
-      <c r="C273" t="inlineStr">
-        <is>
-          <t>25351314668202468</t>
-        </is>
+      <c r="C273" t="n">
+        <v>2.535131466820247e+16</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -7798,10 +7254,8 @@
           <t>minoxidil</t>
         </is>
       </c>
-      <c r="C274" t="inlineStr">
-        <is>
-          <t>25351574782202364</t>
-        </is>
+      <c r="C274" t="n">
+        <v>2.535157478220236e+16</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -7825,10 +7279,8 @@
           <t>estradiol hemi-hidratado</t>
         </is>
       </c>
-      <c r="C275" t="inlineStr">
-        <is>
-          <t>25351499748202301</t>
-        </is>
+      <c r="C275" t="n">
+        <v>2.53514997482023e+16</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -7852,10 +7304,8 @@
           <t>estradiol hemi-hidratado</t>
         </is>
       </c>
-      <c r="C276" t="inlineStr">
-        <is>
-          <t>25351517490202324</t>
-        </is>
+      <c r="C276" t="n">
+        <v>2.535151749020232e+16</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -7879,10 +7329,8 @@
           <t>dapagliflozina</t>
         </is>
       </c>
-      <c r="C277" t="inlineStr">
-        <is>
-          <t>25351219586202419</t>
-        </is>
+      <c r="C277" t="n">
+        <v>2.535121958620242e+16</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -7906,10 +7354,8 @@
           <t>elafibranor</t>
         </is>
       </c>
-      <c r="C278" t="inlineStr">
-        <is>
-          <t>25351068368202400</t>
-        </is>
+      <c r="C278" t="n">
+        <v>2.53510683682024e+16</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -7933,10 +7379,8 @@
           <t>silodosina</t>
         </is>
       </c>
-      <c r="C279" t="inlineStr">
-        <is>
-          <t>25351254249202206</t>
-        </is>
+      <c r="C279" t="n">
+        <v>2.535125424920221e+16</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -7960,10 +7404,8 @@
           <t>metotrexato</t>
         </is>
       </c>
-      <c r="C280" t="inlineStr">
-        <is>
-          <t>25351371358202441</t>
-        </is>
+      <c r="C280" t="n">
+        <v>2.535137135820244e+16</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -7987,10 +7429,8 @@
           <t>guaifenesina</t>
         </is>
       </c>
-      <c r="C281" t="inlineStr">
-        <is>
-          <t>25351478629202315</t>
-        </is>
+      <c r="C281" t="n">
+        <v>2.535147862920232e+16</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -8014,10 +7454,8 @@
           <t>minoxidil</t>
         </is>
       </c>
-      <c r="C282" t="inlineStr">
-        <is>
-          <t>25351263421202395</t>
-        </is>
+      <c r="C282" t="n">
+        <v>2.53512634212024e+16</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -8041,10 +7479,8 @@
           <t>maleato de fluvoxamina</t>
         </is>
       </c>
-      <c r="C283" t="inlineStr">
-        <is>
-          <t>25351284880202493</t>
-        </is>
+      <c r="C283" t="n">
+        <v>2.535128488020249e+16</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -8068,10 +7504,8 @@
           <t>clascoterona</t>
         </is>
       </c>
-      <c r="C284" t="inlineStr">
-        <is>
-          <t>25351125416202466</t>
-        </is>
+      <c r="C284" t="n">
+        <v>2.535112541620246e+16</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -8095,10 +7529,8 @@
           <t>metronidazol</t>
         </is>
       </c>
-      <c r="C285" t="inlineStr">
-        <is>
-          <t>25351032545202321</t>
-        </is>
+      <c r="C285" t="n">
+        <v>2.535103254520232e+16</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -8122,10 +7554,8 @@
           <t>mesilato de lazertinibe monoidratado</t>
         </is>
       </c>
-      <c r="C286" t="inlineStr">
-        <is>
-          <t>25351822990202385</t>
-        </is>
+      <c r="C286" t="n">
+        <v>2.535182299020238e+16</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -8149,10 +7579,8 @@
           <t>mesilato de lazertinibe monoidratado</t>
         </is>
       </c>
-      <c r="C287" t="inlineStr">
-        <is>
-          <t>25351434685202411</t>
-        </is>
+      <c r="C287" t="n">
+        <v>2.535143468520241e+16</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -8176,10 +7604,8 @@
           <t>estradiol hemi-hidratado</t>
         </is>
       </c>
-      <c r="C288" t="inlineStr">
-        <is>
-          <t>25351071608202445</t>
-        </is>
+      <c r="C288" t="n">
+        <v>2.535107160820244e+16</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -8203,10 +7629,8 @@
           <t>mesilato de eribulina</t>
         </is>
       </c>
-      <c r="C289" t="inlineStr">
-        <is>
-          <t>25351034145202511</t>
-        </is>
+      <c r="C289" t="n">
+        <v>2.535103414520251e+16</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -8230,10 +7654,8 @@
           <t>loratadina</t>
         </is>
       </c>
-      <c r="C290" t="inlineStr">
-        <is>
-          <t>25351149450202345</t>
-        </is>
+      <c r="C290" t="n">
+        <v>2.535114945020234e+16</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -8257,10 +7679,8 @@
           <t>claritromicina</t>
         </is>
       </c>
-      <c r="C291" t="inlineStr">
-        <is>
-          <t>25351225981202261</t>
-        </is>
+      <c r="C291" t="n">
+        <v>2.535122598120226e+16</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -8284,10 +7704,8 @@
           <t>cetoconazol</t>
         </is>
       </c>
-      <c r="C292" t="inlineStr">
-        <is>
-          <t>25351091055202447</t>
-        </is>
+      <c r="C292" t="n">
+        <v>2.535109105520245e+16</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -8311,10 +7729,8 @@
           <t>fosfato de fludarabina</t>
         </is>
       </c>
-      <c r="C293" t="inlineStr">
-        <is>
-          <t>25351360288202403</t>
-        </is>
+      <c r="C293" t="n">
+        <v>2.53513602882024e+16</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -8338,10 +7754,8 @@
           <t>adapaleno</t>
         </is>
       </c>
-      <c r="C294" t="inlineStr">
-        <is>
-          <t>25351081775202402</t>
-        </is>
+      <c r="C294" t="n">
+        <v>2.53510817752024e+16</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -8365,10 +7779,8 @@
           <t>etinilestradiol</t>
         </is>
       </c>
-      <c r="C295" t="inlineStr">
-        <is>
-          <t>25351351831202210</t>
-        </is>
+      <c r="C295" t="n">
+        <v>2.535135183120221e+16</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -8392,10 +7804,8 @@
           <t>dapagliflozina</t>
         </is>
       </c>
-      <c r="C296" t="inlineStr">
-        <is>
-          <t>25351894250202421</t>
-        </is>
+      <c r="C296" t="n">
+        <v>2.535189425020242e+16</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -8419,10 +7829,8 @@
           <t>acetato de ganirrelix</t>
         </is>
       </c>
-      <c r="C297" t="inlineStr">
-        <is>
-          <t>25351199473202481</t>
-        </is>
+      <c r="C297" t="n">
+        <v>2.535119947320248e+16</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -8446,10 +7854,8 @@
           <t>cloridrato de venlafaxina</t>
         </is>
       </c>
-      <c r="C298" t="inlineStr">
-        <is>
-          <t>25351255406202373</t>
-        </is>
+      <c r="C298" t="n">
+        <v>2.535125540620237e+16</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -8473,10 +7879,8 @@
           <t>drospirenona</t>
         </is>
       </c>
-      <c r="C299" t="inlineStr">
-        <is>
-          <t>25351670318202306</t>
-        </is>
+      <c r="C299" t="n">
+        <v>2.53516703182023e+16</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -8500,10 +7904,8 @@
           <t>carboplatina</t>
         </is>
       </c>
-      <c r="C300" t="inlineStr">
-        <is>
-          <t>25351155916202180</t>
-        </is>
+      <c r="C300" t="n">
+        <v>2.535115591620218e+16</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -8527,10 +7929,8 @@
           <t>omaveloxolona</t>
         </is>
       </c>
-      <c r="C301" t="inlineStr">
-        <is>
-          <t>25351067441202418</t>
-        </is>
+      <c r="C301" t="n">
+        <v>2.535106744120242e+16</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -8554,10 +7954,8 @@
           <t>nimesulida</t>
         </is>
       </c>
-      <c r="C302" t="inlineStr">
-        <is>
-          <t>25351191512202231</t>
-        </is>
+      <c r="C302" t="n">
+        <v>2.535119151220223e+16</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -8581,10 +7979,8 @@
           <t>naproxeno sódico</t>
         </is>
       </c>
-      <c r="C303" t="inlineStr">
-        <is>
-          <t>25351749917202351</t>
-        </is>
+      <c r="C303" t="n">
+        <v>2.535174991720235e+16</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -8608,10 +8004,8 @@
           <t>cloridrato de bupropiona</t>
         </is>
       </c>
-      <c r="C304" t="inlineStr">
-        <is>
-          <t>25351497489202376</t>
-        </is>
+      <c r="C304" t="n">
+        <v>2.535149748920238e+16</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -8635,10 +8029,8 @@
           <t>ivacaftor</t>
         </is>
       </c>
-      <c r="C305" t="inlineStr">
-        <is>
-          <t>25351361785202330</t>
-        </is>
+      <c r="C305" t="n">
+        <v>2.535136178520233e+16</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -8662,10 +8054,8 @@
           <t>ácido hemicítrico vorasidenibe hemi-hidratado</t>
         </is>
       </c>
-      <c r="C306" t="inlineStr">
-        <is>
-          <t>25351847477202305</t>
-        </is>
+      <c r="C306" t="n">
+        <v>2.53518474772023e+16</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -8689,10 +8079,8 @@
           <t>mesilato de safinamida</t>
         </is>
       </c>
-      <c r="C307" t="inlineStr">
-        <is>
-          <t>25351266164202424</t>
-        </is>
+      <c r="C307" t="n">
+        <v>2.535126616420242e+16</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -8716,10 +8104,8 @@
           <t>mesilato de safinamida</t>
         </is>
       </c>
-      <c r="C308" t="inlineStr">
-        <is>
-          <t>25351183937202438</t>
-        </is>
+      <c r="C308" t="n">
+        <v>2.535118393720244e+16</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -8743,10 +8129,8 @@
           <t>cloridrato de metilfenidato</t>
         </is>
       </c>
-      <c r="C309" t="inlineStr">
-        <is>
-          <t>25351419172202480</t>
-        </is>
+      <c r="C309" t="n">
+        <v>2.535141917220248e+16</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -8770,10 +8154,8 @@
           <t>cloridrato de bupropiona</t>
         </is>
       </c>
-      <c r="C310" t="inlineStr">
-        <is>
-          <t>25351497376202371</t>
-        </is>
+      <c r="C310" t="n">
+        <v>2.535149737620237e+16</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -8797,10 +8179,8 @@
           <t>maleato de clorfeniramina</t>
         </is>
       </c>
-      <c r="C311" t="inlineStr">
-        <is>
-          <t>25351497378202360</t>
-        </is>
+      <c r="C311" t="n">
+        <v>2.535149737820236e+16</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -8824,10 +8204,8 @@
           <t>cloridrato  de ondansetrona di-hidratado</t>
         </is>
       </c>
-      <c r="C312" t="inlineStr">
-        <is>
-          <t>25351717493202366</t>
-        </is>
+      <c r="C312" t="n">
+        <v>2.535171749320237e+16</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -8851,10 +8229,8 @@
           <t>mesilato de belumosudil</t>
         </is>
       </c>
-      <c r="C313" t="inlineStr">
-        <is>
-          <t>25351850099202339</t>
-        </is>
+      <c r="C313" t="n">
+        <v>2.535185009920234e+16</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -8878,10 +8254,8 @@
           <t>lacosamida</t>
         </is>
       </c>
-      <c r="C314" t="inlineStr">
-        <is>
-          <t>25351416725202442</t>
-        </is>
+      <c r="C314" t="n">
+        <v>2.535141672520244e+16</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -8905,10 +8279,8 @@
           <t>azacitidina</t>
         </is>
       </c>
-      <c r="C315" t="inlineStr">
-        <is>
-          <t>25351851435202107</t>
-        </is>
+      <c r="C315" t="n">
+        <v>2.535185143520211e+16</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -8932,10 +8304,8 @@
           <t>ácido azelaico</t>
         </is>
       </c>
-      <c r="C316" t="inlineStr">
-        <is>
-          <t>25351479418202391</t>
-        </is>
+      <c r="C316" t="n">
+        <v>2.535147941820239e+16</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -8959,10 +8329,8 @@
           <t>cloridrato de dexmedetomidina</t>
         </is>
       </c>
-      <c r="C317" t="inlineStr">
-        <is>
-          <t>25351289617202229</t>
-        </is>
+      <c r="C317" t="n">
+        <v>2.535128961720223e+16</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -8986,10 +8354,8 @@
           <t>undecilato de testosterona</t>
         </is>
       </c>
-      <c r="C318" t="inlineStr">
-        <is>
-          <t>25351629018202333</t>
-        </is>
+      <c r="C318" t="n">
+        <v>2.535162901820233e+16</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -9013,10 +8379,8 @@
           <t>diclofenaco</t>
         </is>
       </c>
-      <c r="C319" t="inlineStr">
-        <is>
-          <t>25351453693202113</t>
-        </is>
+      <c r="C319" t="n">
+        <v>2.535145369320211e+16</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -9040,10 +8404,8 @@
           <t>cloridrato de olopatadina</t>
         </is>
       </c>
-      <c r="C320" t="inlineStr">
-        <is>
-          <t>25351637549202308</t>
-        </is>
+      <c r="C320" t="n">
+        <v>2.535163754920231e+16</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -9067,10 +8429,8 @@
           <t>cloridrato de oxomemazina</t>
         </is>
       </c>
-      <c r="C321" t="inlineStr">
-        <is>
-          <t>25351388057202375</t>
-        </is>
+      <c r="C321" t="n">
+        <v>2.535138805720238e+16</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -9094,10 +8454,8 @@
           <t>adapaleno</t>
         </is>
       </c>
-      <c r="C322" t="inlineStr">
-        <is>
-          <t>25351077930202488</t>
-        </is>
+      <c r="C322" t="n">
+        <v>2.535107793020249e+16</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -9121,10 +8479,8 @@
           <t>sugamadex sódico</t>
         </is>
       </c>
-      <c r="C323" t="inlineStr">
-        <is>
-          <t>25351919670202002</t>
-        </is>
+      <c r="C323" t="n">
+        <v>2.5351919670202e+16</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -9148,10 +8504,8 @@
           <t>flurbiprofeno</t>
         </is>
       </c>
-      <c r="C324" t="inlineStr">
-        <is>
-          <t>25351345381202307</t>
-        </is>
+      <c r="C324" t="n">
+        <v>2.535134538120231e+16</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -9175,10 +8529,8 @@
           <t>cloreto de maralixibate</t>
         </is>
       </c>
-      <c r="C325" t="inlineStr">
-        <is>
-          <t>25351563718202358</t>
-        </is>
+      <c r="C325" t="n">
+        <v>2.535156371820236e+16</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -9202,10 +8554,8 @@
           <t>guaifenesina</t>
         </is>
       </c>
-      <c r="C326" t="inlineStr">
-        <is>
-          <t>25351525011202343</t>
-        </is>
+      <c r="C326" t="n">
+        <v>2.535152501120234e+16</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -9229,10 +8579,8 @@
           <t>propilenoglicolato de darunavir</t>
         </is>
       </c>
-      <c r="C327" t="inlineStr">
-        <is>
-          <t>25351243842202308</t>
-        </is>
+      <c r="C327" t="n">
+        <v>2.535124384220231e+16</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -9256,10 +8604,8 @@
           <t>cloridrato de dorzolamida</t>
         </is>
       </c>
-      <c r="C328" t="inlineStr">
-        <is>
-          <t>25351096021202287</t>
-        </is>
+      <c r="C328" t="n">
+        <v>2.535109602120229e+16</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -9283,10 +8629,8 @@
           <t>dicloridrato de meclozina monoidratado</t>
         </is>
       </c>
-      <c r="C329" t="inlineStr">
-        <is>
-          <t>25351021199202355</t>
-        </is>
+      <c r="C329" t="n">
+        <v>2.535102119920236e+16</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -9310,10 +8654,8 @@
           <t>ezetimiba</t>
         </is>
       </c>
-      <c r="C330" t="inlineStr">
-        <is>
-          <t>25351345388202230</t>
-        </is>
+      <c r="C330" t="n">
+        <v>2.535134538820223e+16</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -9337,10 +8679,8 @@
           <t>cloridrato de metformina</t>
         </is>
       </c>
-      <c r="C331" t="inlineStr">
-        <is>
-          <t>25351383060202301</t>
-        </is>
+      <c r="C331" t="n">
+        <v>2.53513830602023e+16</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -9364,10 +8704,8 @@
           <t>cloridrato de pazopanibe</t>
         </is>
       </c>
-      <c r="C332" t="inlineStr">
-        <is>
-          <t>25351404992202396</t>
-        </is>
+      <c r="C332" t="n">
+        <v>2.53514049922024e+16</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -9391,10 +8729,8 @@
           <t>levetiracetam</t>
         </is>
       </c>
-      <c r="C333" t="inlineStr">
-        <is>
-          <t>25351811240202388</t>
-        </is>
+      <c r="C333" t="n">
+        <v>2.535181124020239e+16</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -9418,10 +8754,8 @@
           <t>cloridrato de bendamustina monoidratada</t>
         </is>
       </c>
-      <c r="C334" t="inlineStr">
-        <is>
-          <t>25351264757202111</t>
-        </is>
+      <c r="C334" t="n">
+        <v>2.535126475720211e+16</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -9445,10 +8779,8 @@
           <t>cloridrato de olopatadina</t>
         </is>
       </c>
-      <c r="C335" t="inlineStr">
-        <is>
-          <t>25351711668202321</t>
-        </is>
+      <c r="C335" t="n">
+        <v>2.535171166820232e+16</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -9472,10 +8804,8 @@
           <t>lamivudina</t>
         </is>
       </c>
-      <c r="C336" t="inlineStr">
-        <is>
-          <t>25351031578202434</t>
-        </is>
+      <c r="C336" t="n">
+        <v>2.535103157820243e+16</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -9499,10 +8829,8 @@
           <t>diclofenaco sódico</t>
         </is>
       </c>
-      <c r="C337" t="inlineStr">
-        <is>
-          <t>25351739954202190</t>
-        </is>
+      <c r="C337" t="n">
+        <v>2.535173995420219e+16</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -9526,10 +8854,8 @@
           <t>tazobactam</t>
         </is>
       </c>
-      <c r="C338" t="inlineStr">
-        <is>
-          <t>25351072899202316</t>
-        </is>
+      <c r="C338" t="n">
+        <v>2.535107289920232e+16</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -9553,10 +8879,8 @@
           <t>palbociclibe</t>
         </is>
       </c>
-      <c r="C339" t="inlineStr">
-        <is>
-          <t>25351431540202387</t>
-        </is>
+      <c r="C339" t="n">
+        <v>2.535143154020239e+16</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -9580,10 +8904,8 @@
           <t>cetoprofeno</t>
         </is>
       </c>
-      <c r="C340" t="inlineStr">
-        <is>
-          <t>25351514888202228</t>
-        </is>
+      <c r="C340" t="n">
+        <v>2.535151488820223e+16</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -9607,10 +8929,8 @@
           <t>cloridrato de biperideno</t>
         </is>
       </c>
-      <c r="C341" t="inlineStr">
-        <is>
-          <t>25351245563202451</t>
-        </is>
+      <c r="C341" t="n">
+        <v>2.535124556320245e+16</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -9634,10 +8954,8 @@
           <t>elexacaftor</t>
         </is>
       </c>
-      <c r="C342" t="inlineStr">
-        <is>
-          <t>25351361427202327</t>
-        </is>
+      <c r="C342" t="n">
+        <v>2.535136142720233e+16</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -9661,10 +8979,8 @@
           <t>finasterida</t>
         </is>
       </c>
-      <c r="C343" t="inlineStr">
-        <is>
-          <t>25351116666202324</t>
-        </is>
+      <c r="C343" t="n">
+        <v>2.535111666620232e+16</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -9688,10 +9004,8 @@
           <t>lenalidomida</t>
         </is>
       </c>
-      <c r="C344" t="inlineStr">
-        <is>
-          <t>25351590241202383</t>
-        </is>
+      <c r="C344" t="n">
+        <v>2.535159024120238e+16</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -9715,10 +9029,8 @@
           <t>pregabalina</t>
         </is>
       </c>
-      <c r="C345" t="inlineStr">
-        <is>
-          <t>25351459478202215</t>
-        </is>
+      <c r="C345" t="n">
+        <v>2.535145947820222e+16</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -9742,10 +9054,8 @@
           <t>dicloridrato de meclozina monoidratado</t>
         </is>
       </c>
-      <c r="C346" t="inlineStr">
-        <is>
-          <t>25351042255202395</t>
-        </is>
+      <c r="C346" t="n">
+        <v>2.53510422552024e+16</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -9769,10 +9079,8 @@
           <t>cloridrato de iptacopana monoidratado</t>
         </is>
       </c>
-      <c r="C347" t="inlineStr">
-        <is>
-          <t>25351555119202361</t>
-        </is>
+      <c r="C347" t="n">
+        <v>2.535155511920236e+16</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -9796,10 +9104,8 @@
           <t>fumarato de vonoprazana</t>
         </is>
       </c>
-      <c r="C348" t="inlineStr">
-        <is>
-          <t>25351741577202311</t>
-        </is>
+      <c r="C348" t="n">
+        <v>2.535174157720231e+16</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -9823,10 +9129,8 @@
           <t>cloridrato de midazolam</t>
         </is>
       </c>
-      <c r="C349" t="inlineStr">
-        <is>
-          <t>25351462214202231</t>
-        </is>
+      <c r="C349" t="n">
+        <v>2.535146221420223e+16</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -9850,10 +9154,8 @@
           <t>fosfato dissódico de dexametasona</t>
         </is>
       </c>
-      <c r="C350" t="inlineStr">
-        <is>
-          <t>25351197307202360</t>
-        </is>
+      <c r="C350" t="n">
+        <v>2.535119730720236e+16</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -9877,10 +9179,8 @@
           <t>danicopana</t>
         </is>
       </c>
-      <c r="C351" t="inlineStr">
-        <is>
-          <t>25351190257202390</t>
-        </is>
+      <c r="C351" t="n">
+        <v>2.535119025720239e+16</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -9904,10 +9204,8 @@
           <t>cloridrato de lurasidona</t>
         </is>
       </c>
-      <c r="C352" t="inlineStr">
-        <is>
-          <t>25351579766202368</t>
-        </is>
+      <c r="C352" t="n">
+        <v>2.535157976620237e+16</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -9931,10 +9229,8 @@
           <t>eszopiclona</t>
         </is>
       </c>
-      <c r="C353" t="inlineStr">
-        <is>
-          <t>25351822689202371</t>
-        </is>
+      <c r="C353" t="n">
+        <v>2.535182268920237e+16</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -9958,10 +9254,8 @@
           <t>cloridrato de gencitabina</t>
         </is>
       </c>
-      <c r="C354" t="inlineStr">
-        <is>
-          <t>25351351709202235</t>
-        </is>
+      <c r="C354" t="n">
+        <v>2.535135170920224e+16</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -9985,10 +9279,8 @@
           <t>azitromicina di-hidratada</t>
         </is>
       </c>
-      <c r="C355" t="inlineStr">
-        <is>
-          <t>25351517606202244</t>
-        </is>
+      <c r="C355" t="n">
+        <v>2.535151760620224e+16</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -10012,10 +9304,8 @@
           <t>cloridrato de moxifloxacino monoidratado</t>
         </is>
       </c>
-      <c r="C356" t="inlineStr">
-        <is>
-          <t>25351415106202350</t>
-        </is>
+      <c r="C356" t="n">
+        <v>2.535141510620235e+16</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -10039,10 +9329,8 @@
           <t>cloridrato de palonosetrona</t>
         </is>
       </c>
-      <c r="C357" t="inlineStr">
-        <is>
-          <t>25351860688202325</t>
-        </is>
+      <c r="C357" t="n">
+        <v>2.535186068820232e+16</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -10066,10 +9354,8 @@
           <t>avacopana</t>
         </is>
       </c>
-      <c r="C358" t="inlineStr">
-        <is>
-          <t>25351416843202370</t>
-        </is>
+      <c r="C358" t="n">
+        <v>2.535141684320237e+16</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -10093,10 +9379,8 @@
           <t>valerato de estradiol</t>
         </is>
       </c>
-      <c r="C359" t="inlineStr">
-        <is>
-          <t>25351506854202341</t>
-        </is>
+      <c r="C359" t="n">
+        <v>2.535150685420234e+16</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -10120,10 +9404,8 @@
           <t>cloridrato de escetamina</t>
         </is>
       </c>
-      <c r="C360" t="inlineStr">
-        <is>
-          <t>25351308822202381</t>
-        </is>
+      <c r="C360" t="n">
+        <v>2.535130882220238e+16</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -10147,10 +9429,8 @@
           <t>sirolimo</t>
         </is>
       </c>
-      <c r="C361" t="inlineStr">
-        <is>
-          <t>25351448752202212</t>
-        </is>
+      <c r="C361" t="n">
+        <v>2.535144875220221e+16</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -10174,10 +9454,8 @@
           <t>nimesulida</t>
         </is>
       </c>
-      <c r="C362" t="inlineStr">
-        <is>
-          <t>25351645221202276</t>
-        </is>
+      <c r="C362" t="n">
+        <v>2.535164522120228e+16</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -10201,10 +9479,8 @@
           <t>bortezomibe</t>
         </is>
       </c>
-      <c r="C363" t="inlineStr">
-        <is>
-          <t>25351635373202180</t>
-        </is>
+      <c r="C363" t="n">
+        <v>2.535163537320218e+16</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -10228,10 +9504,8 @@
           <t>levetiracetam</t>
         </is>
       </c>
-      <c r="C364" t="inlineStr">
-        <is>
-          <t>25351819514202387</t>
-        </is>
+      <c r="C364" t="n">
+        <v>2.535181951420239e+16</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -10255,10 +9529,8 @@
           <t>dicloridrato de trimetazidina</t>
         </is>
       </c>
-      <c r="C365" t="inlineStr">
-        <is>
-          <t>25351171502202289</t>
-        </is>
+      <c r="C365" t="n">
+        <v>2.535117150220229e+16</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -10282,10 +9554,8 @@
           <t>praziquantel</t>
         </is>
       </c>
-      <c r="C366" t="inlineStr">
-        <is>
-          <t>25351463953202321</t>
-        </is>
+      <c r="C366" t="n">
+        <v>2.535146395320232e+16</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -10309,10 +9579,8 @@
           <t>bromidrato de vortioxetina</t>
         </is>
       </c>
-      <c r="C367" t="inlineStr">
-        <is>
-          <t>25351581974202327</t>
-        </is>
+      <c r="C367" t="n">
+        <v>2.535158197420233e+16</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -10336,10 +9604,8 @@
           <t>benzoato de alogliptina</t>
         </is>
       </c>
-      <c r="C368" t="inlineStr">
-        <is>
-          <t>25351225839202302</t>
-        </is>
+      <c r="C368" t="n">
+        <v>2.53512258392023e+16</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -10363,10 +9629,8 @@
           <t>finasterida</t>
         </is>
       </c>
-      <c r="C369" t="inlineStr">
-        <is>
-          <t>25351599839202257</t>
-        </is>
+      <c r="C369" t="n">
+        <v>2.535159983920226e+16</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -10390,10 +9654,8 @@
           <t>fumarato de dimetila</t>
         </is>
       </c>
-      <c r="C370" t="inlineStr">
-        <is>
-          <t>25351855399202312</t>
-        </is>
+      <c r="C370" t="n">
+        <v>2.535185539920231e+16</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -10417,10 +9679,8 @@
           <t>cloridrato de oxicodona</t>
         </is>
       </c>
-      <c r="C371" t="inlineStr">
-        <is>
-          <t>25351417941202243</t>
-        </is>
+      <c r="C371" t="n">
+        <v>2.535141794120224e+16</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -10444,10 +9704,8 @@
           <t>mucato de isometepteno</t>
         </is>
       </c>
-      <c r="C372" t="inlineStr">
-        <is>
-          <t>25351582408202251</t>
-        </is>
+      <c r="C372" t="n">
+        <v>2.535158240820225e+16</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -10471,10 +9729,8 @@
           <t>levonorgestrel</t>
         </is>
       </c>
-      <c r="C373" t="inlineStr">
-        <is>
-          <t>25351236616202281</t>
-        </is>
+      <c r="C373" t="n">
+        <v>2.535123661620228e+16</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -10498,10 +9754,8 @@
           <t>ticagrelor</t>
         </is>
       </c>
-      <c r="C374" t="inlineStr">
-        <is>
-          <t>25351425401202314</t>
-        </is>
+      <c r="C374" t="n">
+        <v>2.535142540120231e+16</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -10525,10 +9779,8 @@
           <t>cloridrato de ciclobenzaprina</t>
         </is>
       </c>
-      <c r="C375" t="inlineStr">
-        <is>
-          <t>25351166176202379</t>
-        </is>
+      <c r="C375" t="n">
+        <v>2.535116617620238e+16</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -10552,10 +9804,8 @@
           <t>mirabegrona</t>
         </is>
       </c>
-      <c r="C376" t="inlineStr">
-        <is>
-          <t>25351564538202393</t>
-        </is>
+      <c r="C376" t="n">
+        <v>2.535156453820239e+16</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -10579,10 +9829,8 @@
           <t>ezetimiba</t>
         </is>
       </c>
-      <c r="C377" t="inlineStr">
-        <is>
-          <t>25351220203202285</t>
-        </is>
+      <c r="C377" t="n">
+        <v>2.535122020320228e+16</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -10606,10 +9854,8 @@
           <t>vismodegibe</t>
         </is>
       </c>
-      <c r="C378" t="inlineStr">
-        <is>
-          <t>25351102326202235</t>
-        </is>
+      <c r="C378" t="n">
+        <v>2.535110232620224e+16</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -10633,10 +9879,8 @@
           <t>trometamol cetorolaco</t>
         </is>
       </c>
-      <c r="C379" t="inlineStr">
-        <is>
-          <t>25351244080202014</t>
-        </is>
+      <c r="C379" t="n">
+        <v>2.535124408020202e+16</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -10660,10 +9904,8 @@
           <t>cloridrato de benzidamina</t>
         </is>
       </c>
-      <c r="C380" t="inlineStr">
-        <is>
-          <t>25351555432202218</t>
-        </is>
+      <c r="C380" t="n">
+        <v>2.535155543220222e+16</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -10687,10 +9929,8 @@
           <t>nitrato de miconazol</t>
         </is>
       </c>
-      <c r="C381" t="inlineStr">
-        <is>
-          <t>25351335810202249</t>
-        </is>
+      <c r="C381" t="n">
+        <v>2.535133581020225e+16</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -10714,10 +9954,8 @@
           <t>pemigatinibe</t>
         </is>
       </c>
-      <c r="C382" t="inlineStr">
-        <is>
-          <t>25351309086202389</t>
-        </is>
+      <c r="C382" t="n">
+        <v>2.535130908620239e+16</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -10741,10 +9979,8 @@
           <t>levofloxacino hemi-hidratado</t>
         </is>
       </c>
-      <c r="C383" t="inlineStr">
-        <is>
-          <t>25351014505202135</t>
-        </is>
+      <c r="C383" t="n">
+        <v>2.535101450520214e+16</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -10768,10 +10004,8 @@
           <t>bromidrato de galantamina</t>
         </is>
       </c>
-      <c r="C384" t="inlineStr">
-        <is>
-          <t>25351478422202251</t>
-        </is>
+      <c r="C384" t="n">
+        <v>2.535147842220225e+16</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -10795,10 +10029,8 @@
           <t>dipirona monoidratada</t>
         </is>
       </c>
-      <c r="C385" t="inlineStr">
-        <is>
-          <t>25351626782202276</t>
-        </is>
+      <c r="C385" t="n">
+        <v>2.535162678220228e+16</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -10822,10 +10054,8 @@
           <t>rivaroxabana</t>
         </is>
       </c>
-      <c r="C386" t="inlineStr">
-        <is>
-          <t>25351500435202214</t>
-        </is>
+      <c r="C386" t="n">
+        <v>2.535150043520222e+16</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -10849,10 +10079,8 @@
           <t>cloridrato de buspirona</t>
         </is>
       </c>
-      <c r="C387" t="inlineStr">
-        <is>
-          <t>25351388549202361</t>
-        </is>
+      <c r="C387" t="n">
+        <v>2.535138854920236e+16</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -10876,10 +10104,8 @@
           <t>cloridrato de naltrexona</t>
         </is>
       </c>
-      <c r="C388" t="inlineStr">
-        <is>
-          <t>25351002633202217</t>
-        </is>
+      <c r="C388" t="n">
+        <v>2.535100263320222e+16</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -10903,10 +10129,8 @@
           <t>cloridrato de lurasidona</t>
         </is>
       </c>
-      <c r="C389" t="inlineStr">
-        <is>
-          <t>25351501810202243</t>
-        </is>
+      <c r="C389" t="n">
+        <v>2.535150181020224e+16</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -10930,10 +10154,8 @@
           <t>piperacilina monoidratada</t>
         </is>
       </c>
-      <c r="C390" t="inlineStr">
-        <is>
-          <t>25351072898202363</t>
-        </is>
+      <c r="C390" t="n">
+        <v>2.535107289820236e+16</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -10957,10 +10179,8 @@
           <t>cloridrato de tramadol</t>
         </is>
       </c>
-      <c r="C391" t="inlineStr">
-        <is>
-          <t>25351582994202234</t>
-        </is>
+      <c r="C391" t="n">
+        <v>2.535158299420223e+16</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -10984,10 +10204,8 @@
           <t>ácido ursodesoxicólico</t>
         </is>
       </c>
-      <c r="C392" t="inlineStr">
-        <is>
-          <t>25351398922202391</t>
-        </is>
+      <c r="C392" t="n">
+        <v>2.535139892220239e+16</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -11011,10 +10229,8 @@
           <t>aciclovir</t>
         </is>
       </c>
-      <c r="C393" t="inlineStr">
-        <is>
-          <t>25351526336202262</t>
-        </is>
+      <c r="C393" t="n">
+        <v>2.535152633620226e+16</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -11038,10 +10254,8 @@
           <t>fenofibrato</t>
         </is>
       </c>
-      <c r="C394" t="inlineStr">
-        <is>
-          <t>25351604683202233</t>
-        </is>
+      <c r="C394" t="n">
+        <v>2.535160468320223e+16</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -11065,10 +10279,8 @@
           <t>clavulanato de potássio</t>
         </is>
       </c>
-      <c r="C395" t="inlineStr">
-        <is>
-          <t>25351199805202347</t>
-        </is>
+      <c r="C395" t="n">
+        <v>2.535119980520235e+16</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -11092,10 +10304,8 @@
           <t>levetiracetam</t>
         </is>
       </c>
-      <c r="C396" t="inlineStr">
-        <is>
-          <t>25351229934202377</t>
-        </is>
+      <c r="C396" t="n">
+        <v>2.535122993420238e+16</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -11119,10 +10329,8 @@
           <t>ceftriaxona dissódica hemieptaidratada</t>
         </is>
       </c>
-      <c r="C397" t="inlineStr">
-        <is>
-          <t>25351140907202275</t>
-        </is>
+      <c r="C397" t="n">
+        <v>2.535114090720228e+16</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -11146,10 +10354,8 @@
           <t>glimepirida</t>
         </is>
       </c>
-      <c r="C398" t="inlineStr">
-        <is>
-          <t>25351042814202286</t>
-        </is>
+      <c r="C398" t="n">
+        <v>2.535104281420229e+16</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -11173,10 +10379,8 @@
           <t>topiramato</t>
         </is>
       </c>
-      <c r="C399" t="inlineStr">
-        <is>
-          <t>25351069519202277</t>
-        </is>
+      <c r="C399" t="n">
+        <v>2.535106951920228e+16</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -11200,10 +10404,8 @@
           <t>cloridrato  de ondansetrona di-hidratado</t>
         </is>
       </c>
-      <c r="C400" t="inlineStr">
-        <is>
-          <t>25351567351202341</t>
-        </is>
+      <c r="C400" t="n">
+        <v>2.535156735120234e+16</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -11227,10 +10429,8 @@
           <t>dimesilato de lisdexanfetamina</t>
         </is>
       </c>
-      <c r="C401" t="inlineStr">
-        <is>
-          <t>25351380342202348</t>
-        </is>
+      <c r="C401" t="n">
+        <v>2.535138034220235e+16</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -11254,10 +10454,8 @@
           <t>cloridrato de naltrexona</t>
         </is>
       </c>
-      <c r="C402" t="inlineStr">
-        <is>
-          <t>25351106351202298</t>
-        </is>
+      <c r="C402" t="n">
+        <v>2.53511063512023e+16</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -11281,10 +10479,8 @@
           <t>levetiracetam</t>
         </is>
       </c>
-      <c r="C403" t="inlineStr">
-        <is>
-          <t>25351302018202399</t>
-        </is>
+      <c r="C403" t="n">
+        <v>2.53513020182024e+16</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -11308,10 +10504,8 @@
           <t>fumarato de vonoprazana</t>
         </is>
       </c>
-      <c r="C404" t="inlineStr">
-        <is>
-          <t>25351807440202336</t>
-        </is>
+      <c r="C404" t="n">
+        <v>2.535180744020234e+16</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -11335,10 +10529,8 @@
           <t>dimesilato de lisdexanfetamina</t>
         </is>
       </c>
-      <c r="C405" t="inlineStr">
-        <is>
-          <t>25351425844202313</t>
-        </is>
+      <c r="C405" t="n">
+        <v>2.535142584420231e+16</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -11362,10 +10554,8 @@
           <t>loxoprofeno sódico di-hidratado</t>
         </is>
       </c>
-      <c r="C406" t="inlineStr">
-        <is>
-          <t>25351214974202314</t>
-        </is>
+      <c r="C406" t="n">
+        <v>2.535121497420231e+16</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -11389,10 +10579,8 @@
           <t>palmitato de paliperidona</t>
         </is>
       </c>
-      <c r="C407" t="inlineStr">
-        <is>
-          <t>25351603386202271</t>
-        </is>
+      <c r="C407" t="n">
+        <v>2.535160338620227e+16</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -11416,10 +10604,8 @@
           <t>hemifumarato de quetiapina</t>
         </is>
       </c>
-      <c r="C408" t="inlineStr">
-        <is>
-          <t>25351845681202111</t>
-        </is>
+      <c r="C408" t="n">
+        <v>2.535184568120211e+16</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -11443,10 +10629,8 @@
           <t>ivermectina</t>
         </is>
       </c>
-      <c r="C409" t="inlineStr">
-        <is>
-          <t>25351466676202227</t>
-        </is>
+      <c r="C409" t="n">
+        <v>2.535146667620223e+16</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -11470,10 +10654,8 @@
           <t>tobramicina</t>
         </is>
       </c>
-      <c r="C410" t="inlineStr">
-        <is>
-          <t>25351503108202214</t>
-        </is>
+      <c r="C410" t="n">
+        <v>2.535150310820222e+16</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -11497,10 +10679,8 @@
           <t>tobramicina</t>
         </is>
       </c>
-      <c r="C411" t="inlineStr">
-        <is>
-          <t>25351503108202214</t>
-        </is>
+      <c r="C411" t="n">
+        <v>2.535150310820222e+16</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -11524,10 +10704,8 @@
           <t>tobramicina</t>
         </is>
       </c>
-      <c r="C412" t="inlineStr">
-        <is>
-          <t>25351503108202214</t>
-        </is>
+      <c r="C412" t="n">
+        <v>2.535150310820222e+16</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -11551,10 +10729,8 @@
           <t>tobramicina</t>
         </is>
       </c>
-      <c r="C413" t="inlineStr">
-        <is>
-          <t>25351503108202214</t>
-        </is>
+      <c r="C413" t="n">
+        <v>2.535150310820222e+16</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -11578,10 +10754,8 @@
           <t>rivaroxabana</t>
         </is>
       </c>
-      <c r="C414" t="inlineStr">
-        <is>
-          <t>25351286729202228</t>
-        </is>
+      <c r="C414" t="n">
+        <v>2.535128672920223e+16</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -11605,10 +10779,8 @@
           <t>latanoprosta</t>
         </is>
       </c>
-      <c r="C415" t="inlineStr">
-        <is>
-          <t>25351331626202220</t>
-        </is>
+      <c r="C415" t="n">
+        <v>2.535133162620222e+16</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -11632,10 +10804,8 @@
           <t>maleato de timolol</t>
         </is>
       </c>
-      <c r="C416" t="inlineStr">
-        <is>
-          <t>25351045310202218</t>
-        </is>
+      <c r="C416" t="n">
+        <v>2.535104531020222e+16</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -11659,10 +10829,8 @@
           <t>sugamadex sódico</t>
         </is>
       </c>
-      <c r="C417" t="inlineStr">
-        <is>
-          <t>25351537989202277</t>
-        </is>
+      <c r="C417" t="n">
+        <v>2.535153798920228e+16</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -11686,10 +10854,8 @@
           <t>cloridrato de lurasidona</t>
         </is>
       </c>
-      <c r="C418" t="inlineStr">
-        <is>
-          <t>25351672663202112</t>
-        </is>
+      <c r="C418" t="n">
+        <v>2.535167266320211e+16</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -11713,10 +10879,8 @@
           <t>tartarato de brimonidina</t>
         </is>
       </c>
-      <c r="C419" t="inlineStr">
-        <is>
-          <t>25351274225202265</t>
-        </is>
+      <c r="C419" t="n">
+        <v>2.535127422520226e+16</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -11740,10 +10904,8 @@
           <t>diclofenaco dietilamônio</t>
         </is>
       </c>
-      <c r="C420" t="inlineStr">
-        <is>
-          <t>25351463235202273</t>
-        </is>
+      <c r="C420" t="n">
+        <v>2.535146323520227e+16</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -11767,10 +10929,8 @@
           <t>trometamol cetorolaco</t>
         </is>
       </c>
-      <c r="C421" t="inlineStr">
-        <is>
-          <t>25351220709202294</t>
-        </is>
+      <c r="C421" t="n">
+        <v>2.53512207092023e+16</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -11794,10 +10954,8 @@
           <t>bromoprida</t>
         </is>
       </c>
-      <c r="C422" t="inlineStr">
-        <is>
-          <t>25351414658202260</t>
-        </is>
+      <c r="C422" t="n">
+        <v>2.535141465820226e+16</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -11821,10 +10979,8 @@
           <t>vildagliptina</t>
         </is>
       </c>
-      <c r="C423" t="inlineStr">
-        <is>
-          <t>25351254242202286</t>
-        </is>
+      <c r="C423" t="n">
+        <v>2.535125424220229e+16</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -11848,10 +11004,8 @@
           <t>malato de sunitinibe</t>
         </is>
       </c>
-      <c r="C424" t="inlineStr">
-        <is>
-          <t>25351181549202331</t>
-        </is>
+      <c r="C424" t="n">
+        <v>2.535118154920233e+16</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -11875,10 +11029,8 @@
           <t>ciprofloxacino</t>
         </is>
       </c>
-      <c r="C425" t="inlineStr">
-        <is>
-          <t>25351097818202200</t>
-        </is>
+      <c r="C425" t="n">
+        <v>2.53510978182022e+16</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -11902,10 +11054,8 @@
           <t>cloridrato de ciprofloxacino monoidratado</t>
         </is>
       </c>
-      <c r="C426" t="inlineStr">
-        <is>
-          <t>25351386512202306</t>
-        </is>
+      <c r="C426" t="n">
+        <v>2.53513865122023e+16</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -11929,10 +11079,8 @@
           <t>cloridrato de bendamustina monoidratada</t>
         </is>
       </c>
-      <c r="C427" t="inlineStr">
-        <is>
-          <t>25351631373202119</t>
-        </is>
+      <c r="C427" t="n">
+        <v>2.535163137320212e+16</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -11956,10 +11104,8 @@
           <t>bussulfano</t>
         </is>
       </c>
-      <c r="C428" t="inlineStr">
-        <is>
-          <t>25351097388202218</t>
-        </is>
+      <c r="C428" t="n">
+        <v>2.535109738820222e+16</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -11983,10 +11129,8 @@
           <t>rosuvastatina cálcica</t>
         </is>
       </c>
-      <c r="C429" t="inlineStr">
-        <is>
-          <t>25351591789202260</t>
-        </is>
+      <c r="C429" t="n">
+        <v>2.535159178920226e+16</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -12010,10 +11154,8 @@
           <t>cloridrato de trazodona</t>
         </is>
       </c>
-      <c r="C430" t="inlineStr">
-        <is>
-          <t>25351490239202224</t>
-        </is>
+      <c r="C430" t="n">
+        <v>2.535149023920222e+16</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -12037,10 +11179,8 @@
           <t>cafeína</t>
         </is>
       </c>
-      <c r="C431" t="inlineStr">
-        <is>
-          <t>25351260915202237</t>
-        </is>
+      <c r="C431" t="n">
+        <v>2.535126091520224e+16</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -12064,10 +11204,8 @@
           <t>cloridrato de metformina</t>
         </is>
       </c>
-      <c r="C432" t="inlineStr">
-        <is>
-          <t>25351031776202236</t>
-        </is>
+      <c r="C432" t="n">
+        <v>2.535103177620224e+16</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -12091,10 +11229,8 @@
           <t>cafeína</t>
         </is>
       </c>
-      <c r="C433" t="inlineStr">
-        <is>
-          <t>25351618790202249</t>
-        </is>
+      <c r="C433" t="n">
+        <v>2.535161879020225e+16</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -12118,10 +11254,8 @@
           <t>benfotiamina</t>
         </is>
       </c>
-      <c r="C434" t="inlineStr">
-        <is>
-          <t>25351115898202365</t>
-        </is>
+      <c r="C434" t="n">
+        <v>2.535111589820236e+16</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -12145,10 +11279,8 @@
           <t>sugamadex sódico</t>
         </is>
       </c>
-      <c r="C435" t="inlineStr">
-        <is>
-          <t>25351558506202359</t>
-        </is>
+      <c r="C435" t="n">
+        <v>2.535155850620236e+16</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -12172,10 +11304,8 @@
           <t>gliclazida</t>
         </is>
       </c>
-      <c r="C436" t="inlineStr">
-        <is>
-          <t>25351351922202247</t>
-        </is>
+      <c r="C436" t="n">
+        <v>2.535135192220225e+16</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -12199,10 +11329,8 @@
           <t>sugamadex sódico</t>
         </is>
       </c>
-      <c r="C437" t="inlineStr">
-        <is>
-          <t>25351514485202289</t>
-        </is>
+      <c r="C437" t="n">
+        <v>2.535151448520229e+16</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -12226,10 +11354,8 @@
           <t>dapagliflozina</t>
         </is>
       </c>
-      <c r="C438" t="inlineStr">
-        <is>
-          <t>25351090758202296</t>
-        </is>
+      <c r="C438" t="n">
+        <v>2.53510907582023e+16</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -12253,10 +11379,8 @@
           <t>claritromicina</t>
         </is>
       </c>
-      <c r="C439" t="inlineStr">
-        <is>
-          <t>25351082643202228</t>
-        </is>
+      <c r="C439" t="n">
+        <v>2.535108264320223e+16</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -12280,10 +11404,8 @@
           <t>linagliptina</t>
         </is>
       </c>
-      <c r="C440" t="inlineStr">
-        <is>
-          <t>25351923314202166</t>
-        </is>
+      <c r="C440" t="n">
+        <v>2.535192331420217e+16</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -12307,10 +11429,8 @@
           <t>bilastina</t>
         </is>
       </c>
-      <c r="C441" t="inlineStr">
-        <is>
-          <t>25351010782202331</t>
-        </is>
+      <c r="C441" t="n">
+        <v>2.535101078220233e+16</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -12334,10 +11454,8 @@
           <t>etodolaco</t>
         </is>
       </c>
-      <c r="C442" t="inlineStr">
-        <is>
-          <t>25351019323202231</t>
-        </is>
+      <c r="C442" t="n">
+        <v>2.535101932320223e+16</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -12361,10 +11479,8 @@
           <t>desloratadina</t>
         </is>
       </c>
-      <c r="C443" t="inlineStr">
-        <is>
-          <t>25351120956202291</t>
-        </is>
+      <c r="C443" t="n">
+        <v>2.535112095620229e+16</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -12388,10 +11504,8 @@
           <t>vildagliptina</t>
         </is>
       </c>
-      <c r="C444" t="inlineStr">
-        <is>
-          <t>25351631107202269</t>
-        </is>
+      <c r="C444" t="n">
+        <v>2.535163110720227e+16</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -12415,10 +11529,8 @@
           <t>ibrutinibe</t>
         </is>
       </c>
-      <c r="C445" t="inlineStr">
-        <is>
-          <t>25351161141202343</t>
-        </is>
+      <c r="C445" t="n">
+        <v>2.535116114120234e+16</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -12442,10 +11554,8 @@
           <t>hemifumarato de quetiapina</t>
         </is>
       </c>
-      <c r="C446" t="inlineStr">
-        <is>
-          <t>25351127200202273</t>
-        </is>
+      <c r="C446" t="n">
+        <v>2.535112720020227e+16</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -12469,10 +11579,8 @@
           <t>ondansetrona</t>
         </is>
       </c>
-      <c r="C447" t="inlineStr">
-        <is>
-          <t>25351143111202274</t>
-        </is>
+      <c r="C447" t="n">
+        <v>2.535114311120227e+16</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -12496,10 +11604,8 @@
           <t>rivaroxabana</t>
         </is>
       </c>
-      <c r="C448" t="inlineStr">
-        <is>
-          <t>25351176871202268</t>
-        </is>
+      <c r="C448" t="n">
+        <v>2.535117687120227e+16</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -12523,10 +11629,8 @@
           <t>dienogeste</t>
         </is>
       </c>
-      <c r="C449" t="inlineStr">
-        <is>
-          <t>25351497379202312</t>
-        </is>
+      <c r="C449" t="n">
+        <v>2.535149737920231e+16</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -12550,10 +11654,8 @@
           <t>bimatoprosta</t>
         </is>
       </c>
-      <c r="C450" t="inlineStr">
-        <is>
-          <t>25351254307202293</t>
-        </is>
+      <c r="C450" t="n">
+        <v>2.535125430720229e+16</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -12577,10 +11679,8 @@
           <t>palbociclibe</t>
         </is>
       </c>
-      <c r="C451" t="inlineStr">
-        <is>
-          <t>25351244335202201</t>
-        </is>
+      <c r="C451" t="n">
+        <v>2.53512443352022e+16</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -12604,10 +11704,8 @@
           <t>ibuprofeno</t>
         </is>
       </c>
-      <c r="C452" t="inlineStr">
-        <is>
-          <t>25351582712202207</t>
-        </is>
+      <c r="C452" t="n">
+        <v>2.535158271220221e+16</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -12631,10 +11729,8 @@
           <t>valerato de estradiol</t>
         </is>
       </c>
-      <c r="C453" t="inlineStr">
-        <is>
-          <t>25351325427202363</t>
-        </is>
+      <c r="C453" t="n">
+        <v>2.535132542720236e+16</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -12658,10 +11754,8 @@
           <t>cloridrato de ciprofloxacino monoidratado</t>
         </is>
       </c>
-      <c r="C454" t="inlineStr">
-        <is>
-          <t>25351441102202246</t>
-        </is>
+      <c r="C454" t="n">
+        <v>2.535144110220225e+16</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -12685,10 +11779,8 @@
           <t>bimatoprosta</t>
         </is>
       </c>
-      <c r="C455" t="inlineStr">
-        <is>
-          <t>25351403161202216</t>
-        </is>
+      <c r="C455" t="n">
+        <v>2.535140316120222e+16</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -12712,10 +11804,8 @@
           <t>trometamol cetorolaco</t>
         </is>
       </c>
-      <c r="C456" t="inlineStr">
-        <is>
-          <t>25351197420202264</t>
-        </is>
+      <c r="C456" t="n">
+        <v>2.535119742020226e+16</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -12739,10 +11829,8 @@
           <t>cloridrato de sitagliptina monoidratado</t>
         </is>
       </c>
-      <c r="C457" t="inlineStr">
-        <is>
-          <t>25351152535202220</t>
-        </is>
+      <c r="C457" t="n">
+        <v>2.535115253520222e+16</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -12766,10 +11854,8 @@
           <t>rivaroxabana</t>
         </is>
       </c>
-      <c r="C458" t="inlineStr">
-        <is>
-          <t>25351129975202364</t>
-        </is>
+      <c r="C458" t="n">
+        <v>2.535112997520236e+16</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -12793,10 +11879,8 @@
           <t>dimenidrinato</t>
         </is>
       </c>
-      <c r="C459" t="inlineStr">
-        <is>
-          <t>25351482939202245</t>
-        </is>
+      <c r="C459" t="n">
+        <v>2.535148293920224e+16</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -12820,10 +11904,8 @@
           <t>rivaroxabana</t>
         </is>
       </c>
-      <c r="C460" t="inlineStr">
-        <is>
-          <t>25351132413202217</t>
-        </is>
+      <c r="C460" t="n">
+        <v>2.535113241320222e+16</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -12847,10 +11929,8 @@
           <t>carbamazepina</t>
         </is>
       </c>
-      <c r="C461" t="inlineStr">
-        <is>
-          <t>25351034221202246</t>
-        </is>
+      <c r="C461" t="n">
+        <v>2.535103422120225e+16</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -12874,10 +11954,8 @@
           <t>mesilato de etexilato de dabigatrana</t>
         </is>
       </c>
-      <c r="C462" t="inlineStr">
-        <is>
-          <t>25351602200202266</t>
-        </is>
+      <c r="C462" t="n">
+        <v>2.535160220020226e+16</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -12901,10 +11979,8 @@
           <t>cloridrato de cinacalcete</t>
         </is>
       </c>
-      <c r="C463" t="inlineStr">
-        <is>
-          <t>25351153141202299</t>
-        </is>
+      <c r="C463" t="n">
+        <v>2.53511531412023e+16</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -12928,10 +12004,8 @@
           <t>rivastigmina</t>
         </is>
       </c>
-      <c r="C464" t="inlineStr">
-        <is>
-          <t>25351259219202369</t>
-        </is>
+      <c r="C464" t="n">
+        <v>2.535125921920237e+16</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -12955,10 +12029,8 @@
           <t>hemifumarato de quetiapina</t>
         </is>
       </c>
-      <c r="C465" t="inlineStr">
-        <is>
-          <t>25351285445202214</t>
-        </is>
+      <c r="C465" t="n">
+        <v>2.535128544520222e+16</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -12982,10 +12054,8 @@
           <t>cloridrato de raloxifeno</t>
         </is>
       </c>
-      <c r="C466" t="inlineStr">
-        <is>
-          <t>25351112060202239</t>
-        </is>
+      <c r="C466" t="n">
+        <v>2.535111206020224e+16</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -13009,10 +12079,8 @@
           <t>dicloridrato de trimetazidina</t>
         </is>
       </c>
-      <c r="C467" t="inlineStr">
-        <is>
-          <t>25351243098202252</t>
-        </is>
+      <c r="C467" t="n">
+        <v>2.535124309820225e+16</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -13036,10 +12104,8 @@
           <t>rivaroxabana</t>
         </is>
       </c>
-      <c r="C468" t="inlineStr">
-        <is>
-          <t>25351135445202355</t>
-        </is>
+      <c r="C468" t="n">
+        <v>2.535113544520236e+16</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -13063,10 +12129,8 @@
           <t>etodolaco</t>
         </is>
       </c>
-      <c r="C469" t="inlineStr">
-        <is>
-          <t>25351012214202293</t>
-        </is>
+      <c r="C469" t="n">
+        <v>2.535101221420229e+16</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -13090,10 +12154,8 @@
           <t>maleato de fluvoxamina</t>
         </is>
       </c>
-      <c r="C470" t="inlineStr">
-        <is>
-          <t>25351631366202290</t>
-        </is>
+      <c r="C470" t="n">
+        <v>2.535163136620229e+16</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -13117,10 +12179,8 @@
           <t>ibuprofeno</t>
         </is>
       </c>
-      <c r="C471" t="inlineStr">
-        <is>
-          <t>25351645366202277</t>
-        </is>
+      <c r="C471" t="n">
+        <v>2.535164536620228e+16</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -13144,10 +12204,8 @@
           <t>cloridrato de metformina</t>
         </is>
       </c>
-      <c r="C472" t="inlineStr">
-        <is>
-          <t>25351500405202216</t>
-        </is>
+      <c r="C472" t="n">
+        <v>2.535150040520222e+16</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -13171,10 +12229,8 @@
           <t>azitromicina di-hidratada</t>
         </is>
       </c>
-      <c r="C473" t="inlineStr">
-        <is>
-          <t>25351331698202277</t>
-        </is>
+      <c r="C473" t="n">
+        <v>2.535133169820228e+16</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -13198,10 +12254,8 @@
           <t>pirazinamida</t>
         </is>
       </c>
-      <c r="C474" t="inlineStr">
-        <is>
-          <t>25351204540202225</t>
-        </is>
+      <c r="C474" t="n">
+        <v>2.535120454020222e+16</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -13225,10 +12279,8 @@
           <t>gestodeno</t>
         </is>
       </c>
-      <c r="C475" t="inlineStr">
-        <is>
-          <t>25351380181202210</t>
-        </is>
+      <c r="C475" t="n">
+        <v>2.535138018120221e+16</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -13252,10 +12304,8 @@
           <t>cloridrato de trazodona</t>
         </is>
       </c>
-      <c r="C476" t="inlineStr">
-        <is>
-          <t>25351277460202299</t>
-        </is>
+      <c r="C476" t="n">
+        <v>2.53512774602023e+16</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -13279,10 +12329,8 @@
           <t>cloridrato de nebivolol</t>
         </is>
       </c>
-      <c r="C477" t="inlineStr">
-        <is>
-          <t>25351244023202299</t>
-        </is>
+      <c r="C477" t="n">
+        <v>2.53512440232023e+16</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -13306,10 +12354,8 @@
           <t>carboplatina</t>
         </is>
       </c>
-      <c r="C478" t="inlineStr">
-        <is>
-          <t>25351054996202319</t>
-        </is>
+      <c r="C478" t="n">
+        <v>2.535105499620232e+16</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -13333,10 +12379,8 @@
           <t>propilenoglicolato de darunavir</t>
         </is>
       </c>
-      <c r="C479" t="inlineStr">
-        <is>
-          <t>25351347109202272</t>
-        </is>
+      <c r="C479" t="n">
+        <v>2.535134710920227e+16</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -13360,10 +12404,8 @@
           <t>cloridrato de valaciclovir</t>
         </is>
       </c>
-      <c r="C480" t="inlineStr">
-        <is>
-          <t>25351365239202297</t>
-        </is>
+      <c r="C480" t="n">
+        <v>2.53513652392023e+16</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -13387,10 +12429,8 @@
           <t>rosuvastatina cálcica</t>
         </is>
       </c>
-      <c r="C481" t="inlineStr">
-        <is>
-          <t>25351108158202291</t>
-        </is>
+      <c r="C481" t="n">
+        <v>2.535110815820229e+16</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -13414,10 +12454,8 @@
           <t>etodolaco</t>
         </is>
       </c>
-      <c r="C482" t="inlineStr">
-        <is>
-          <t>25351498688202211</t>
-        </is>
+      <c r="C482" t="n">
+        <v>2.535149868820221e+16</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -13441,10 +12479,8 @@
           <t>rivaroxabana</t>
         </is>
       </c>
-      <c r="C483" t="inlineStr">
-        <is>
-          <t>25351180024202206</t>
-        </is>
+      <c r="C483" t="n">
+        <v>2.535118002420221e+16</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -13468,10 +12504,8 @@
           <t>azacitidina</t>
         </is>
       </c>
-      <c r="C484" t="inlineStr">
-        <is>
-          <t>25351639418202276</t>
-        </is>
+      <c r="C484" t="n">
+        <v>2.535163941820228e+16</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -13495,10 +12529,8 @@
           <t>midostaurina</t>
         </is>
       </c>
-      <c r="C485" t="inlineStr">
-        <is>
-          <t>25351727015202101</t>
-        </is>
+      <c r="C485" t="n">
+        <v>2.53517270152021e+16</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -13522,10 +12554,8 @@
           <t>cloridrato de metilfenidato</t>
         </is>
       </c>
-      <c r="C486" t="inlineStr">
-        <is>
-          <t>25351053889202373</t>
-        </is>
+      <c r="C486" t="n">
+        <v>2.535105388920237e+16</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -13549,10 +12579,8 @@
           <t>tartarato de brimonidina</t>
         </is>
       </c>
-      <c r="C487" t="inlineStr">
-        <is>
-          <t>25351498531202295</t>
-        </is>
+      <c r="C487" t="n">
+        <v>2.53514985312023e+16</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -13576,10 +12604,8 @@
           <t>tafamidis meglumina</t>
         </is>
       </c>
-      <c r="C488" t="inlineStr">
-        <is>
-          <t>25351090422202223</t>
-        </is>
+      <c r="C488" t="n">
+        <v>2.535109042220222e+16</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -13603,10 +12629,8 @@
           <t>cetoprofeno</t>
         </is>
       </c>
-      <c r="C489" t="inlineStr">
-        <is>
-          <t>25351127199202287</t>
-        </is>
+      <c r="C489" t="n">
+        <v>2.535112719920229e+16</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -13630,10 +12654,8 @@
           <t>latanoprosta</t>
         </is>
       </c>
-      <c r="C490" t="inlineStr">
-        <is>
-          <t>25351147798202306</t>
-        </is>
+      <c r="C490" t="n">
+        <v>2.53511477982023e+16</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -13657,10 +12679,8 @@
           <t>budesonida</t>
         </is>
       </c>
-      <c r="C491" t="inlineStr">
-        <is>
-          <t>25351152957202203</t>
-        </is>
+      <c r="C491" t="n">
+        <v>2.53511529572022e+16</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -13684,10 +12704,8 @@
           <t>ritonavir</t>
         </is>
       </c>
-      <c r="C492" t="inlineStr">
-        <is>
-          <t>25351389816202236</t>
-        </is>
+      <c r="C492" t="n">
+        <v>2.535138981620224e+16</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -13711,10 +12729,8 @@
           <t>amoxicilina tri-hidratada</t>
         </is>
       </c>
-      <c r="C493" t="inlineStr">
-        <is>
-          <t>25351770682202103</t>
-        </is>
+      <c r="C493" t="n">
+        <v>2.53517706822021e+16</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -13738,10 +12754,8 @@
           <t>sinvastatina</t>
         </is>
       </c>
-      <c r="C494" t="inlineStr">
-        <is>
-          <t>25351171106202251</t>
-        </is>
+      <c r="C494" t="n">
+        <v>2.535117110620225e+16</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -13765,10 +12779,8 @@
           <t>sulfato de morfina pentaidratado</t>
         </is>
       </c>
-      <c r="C495" t="inlineStr">
-        <is>
-          <t>25351257070202111</t>
-        </is>
+      <c r="C495" t="n">
+        <v>2.535125707020211e+16</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -13792,10 +12804,8 @@
           <t>brometo de glicopirrônio</t>
         </is>
       </c>
-      <c r="C496" t="inlineStr">
-        <is>
-          <t>25351015195202257</t>
-        </is>
+      <c r="C496" t="n">
+        <v>2.535101519520226e+16</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -13819,10 +12829,8 @@
           <t>budesonida</t>
         </is>
       </c>
-      <c r="C497" t="inlineStr">
-        <is>
-          <t>25351036030202219</t>
-        </is>
+      <c r="C497" t="n">
+        <v>2.535103603020222e+16</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -13846,10 +12854,8 @@
           <t>rivaroxabana</t>
         </is>
       </c>
-      <c r="C498" t="inlineStr">
-        <is>
-          <t>25351039142202221</t>
-        </is>
+      <c r="C498" t="n">
+        <v>2.535103914220222e+16</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -13873,10 +12879,8 @@
           <t>montelucaste de sódio</t>
         </is>
       </c>
-      <c r="C499" t="inlineStr">
-        <is>
-          <t>25351796853202116</t>
-        </is>
+      <c r="C499" t="n">
+        <v>2.535179685320212e+16</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -13900,10 +12904,8 @@
           <t>sugamadex sódico</t>
         </is>
       </c>
-      <c r="C500" t="inlineStr">
-        <is>
-          <t>25351779849202193</t>
-        </is>
+      <c r="C500" t="n">
+        <v>2.535177984920219e+16</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -13927,10 +12929,8 @@
           <t>maleato de timolol</t>
         </is>
       </c>
-      <c r="C501" t="inlineStr">
-        <is>
-          <t>25351087503202246</t>
-        </is>
+      <c r="C501" t="n">
+        <v>2.535108750320225e+16</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -13954,10 +12954,8 @@
           <t>micafungina sódica</t>
         </is>
       </c>
-      <c r="C502" t="inlineStr">
-        <is>
-          <t>25351543525202208</t>
-        </is>
+      <c r="C502" t="n">
+        <v>2.535154352520221e+16</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -13981,10 +12979,8 @@
           <t>fenitoína</t>
         </is>
       </c>
-      <c r="C503" t="inlineStr">
-        <is>
-          <t>25351122886202214</t>
-        </is>
+      <c r="C503" t="n">
+        <v>2.535112288620222e+16</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -14008,10 +13004,8 @@
           <t>micofenolato de sódio</t>
         </is>
       </c>
-      <c r="C504" t="inlineStr">
-        <is>
-          <t>25351448083202289</t>
-        </is>
+      <c r="C504" t="n">
+        <v>2.535144808320229e+16</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -14035,10 +13029,8 @@
           <t>milrinona</t>
         </is>
       </c>
-      <c r="C505" t="inlineStr">
-        <is>
-          <t>25351038756202296</t>
-        </is>
+      <c r="C505" t="n">
+        <v>2.53510387562023e+16</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -14062,10 +13054,8 @@
           <t>mirtazapina</t>
         </is>
       </c>
-      <c r="C506" t="inlineStr">
-        <is>
-          <t>25351589465202261</t>
-        </is>
+      <c r="C506" t="n">
+        <v>2.535158946520226e+16</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -14089,10 +13079,8 @@
           <t>succinato de metoprolol</t>
         </is>
       </c>
-      <c r="C507" t="inlineStr">
-        <is>
-          <t>25351287504202116</t>
-        </is>
+      <c r="C507" t="n">
+        <v>2.535128750420212e+16</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -14116,10 +13104,8 @@
           <t>etodolaco</t>
         </is>
       </c>
-      <c r="C508" t="inlineStr">
-        <is>
-          <t>25351171112202217</t>
-        </is>
+      <c r="C508" t="n">
+        <v>2.535117111220222e+16</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -14143,10 +13129,8 @@
           <t>vildagliptina</t>
         </is>
       </c>
-      <c r="C509" t="inlineStr">
-        <is>
-          <t>25351407050202289</t>
-        </is>
+      <c r="C509" t="n">
+        <v>2.535140705020229e+16</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -14170,10 +13154,8 @@
           <t>lamotrigina</t>
         </is>
       </c>
-      <c r="C510" t="inlineStr">
-        <is>
-          <t>25351699210202125</t>
-        </is>
+      <c r="C510" t="n">
+        <v>2.535169921020212e+16</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -14197,10 +13179,8 @@
           <t>aciclovir</t>
         </is>
       </c>
-      <c r="C511" t="inlineStr">
-        <is>
-          <t>25351473051202131</t>
-        </is>
+      <c r="C511" t="n">
+        <v>2.535147305120213e+16</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -14224,10 +13204,8 @@
           <t>etanolato de darunavir</t>
         </is>
       </c>
-      <c r="C512" t="inlineStr">
-        <is>
-          <t>25351122285202201</t>
-        </is>
+      <c r="C512" t="n">
+        <v>2.53511222852022e+16</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -14251,10 +13229,8 @@
           <t>lamotrigina</t>
         </is>
       </c>
-      <c r="C513" t="inlineStr">
-        <is>
-          <t>25351171478202288</t>
-        </is>
+      <c r="C513" t="n">
+        <v>2.535117147820229e+16</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -14278,10 +13254,8 @@
           <t>dipirona monoidratada</t>
         </is>
       </c>
-      <c r="C514" t="inlineStr">
-        <is>
-          <t>25351596512202223</t>
-        </is>
+      <c r="C514" t="n">
+        <v>2.535159651220222e+16</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -14305,10 +13279,8 @@
           <t>dasatinibe monoidratado</t>
         </is>
       </c>
-      <c r="C515" t="inlineStr">
-        <is>
-          <t>25351543510202231</t>
-        </is>
+      <c r="C515" t="n">
+        <v>2.535154351020223e+16</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -14332,10 +13304,8 @@
           <t>cloridrato de donepezila monoidratado</t>
         </is>
       </c>
-      <c r="C516" t="inlineStr">
-        <is>
-          <t>25351244345202238</t>
-        </is>
+      <c r="C516" t="n">
+        <v>2.535124434520224e+16</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -14359,10 +13329,8 @@
           <t>adenosina</t>
         </is>
       </c>
-      <c r="C517" t="inlineStr">
-        <is>
-          <t>25351008874202199</t>
-        </is>
+      <c r="C517" t="n">
+        <v>2.53510088742022e+16</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -14386,10 +13354,8 @@
           <t>hemifumarato de bisoprolol</t>
         </is>
       </c>
-      <c r="C518" t="inlineStr">
-        <is>
-          <t>25351618932202197</t>
-        </is>
+      <c r="C518" t="n">
+        <v>2.53516189322022e+16</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -14413,10 +13379,8 @@
           <t>rivaroxabana</t>
         </is>
       </c>
-      <c r="C519" t="inlineStr">
-        <is>
-          <t>25351312133202291</t>
-        </is>
+      <c r="C519" t="n">
+        <v>2.535131213320229e+16</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -14440,10 +13404,8 @@
           <t>bortezomibe</t>
         </is>
       </c>
-      <c r="C520" t="inlineStr">
-        <is>
-          <t>25351839141202107</t>
-        </is>
+      <c r="C520" t="n">
+        <v>2.535183914120211e+16</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -14467,10 +13429,8 @@
           <t>lenalidomida</t>
         </is>
       </c>
-      <c r="C521" t="inlineStr">
-        <is>
-          <t>25351068660202252</t>
-        </is>
+      <c r="C521" t="n">
+        <v>2.535106866020225e+16</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -14494,10 +13454,8 @@
           <t>ampicilina sódica</t>
         </is>
       </c>
-      <c r="C522" t="inlineStr">
-        <is>
-          <t>25351433410202117</t>
-        </is>
+      <c r="C522" t="n">
+        <v>2.535143341020212e+16</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -14521,10 +13479,8 @@
           <t>milrinona</t>
         </is>
       </c>
-      <c r="C523" t="inlineStr">
-        <is>
-          <t>25351869642202118</t>
-        </is>
+      <c r="C523" t="n">
+        <v>2.535186964220212e+16</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -14548,10 +13504,8 @@
           <t>bromidrato de vortioxetina</t>
         </is>
       </c>
-      <c r="C524" t="inlineStr">
-        <is>
-          <t>25351252213202280</t>
-        </is>
+      <c r="C524" t="n">
+        <v>2.535125221320228e+16</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -14575,10 +13529,8 @@
           <t>hemitartarato de zolpidem</t>
         </is>
       </c>
-      <c r="C525" t="inlineStr">
-        <is>
-          <t>25351580744202189</t>
-        </is>
+      <c r="C525" t="n">
+        <v>2.535158074420219e+16</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -14602,10 +13554,8 @@
           <t>aripiprazol</t>
         </is>
       </c>
-      <c r="C526" t="inlineStr">
-        <is>
-          <t>25351524957202210</t>
-        </is>
+      <c r="C526" t="n">
+        <v>2.535152495720221e+16</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -14629,10 +13579,8 @@
           <t>mesilato de lenvatinibe</t>
         </is>
       </c>
-      <c r="C527" t="inlineStr">
-        <is>
-          <t>25351206913202201</t>
-        </is>
+      <c r="C527" t="n">
+        <v>2.53512069132022e+16</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -14656,10 +13604,8 @@
           <t>cloridrato de naratriptana</t>
         </is>
       </c>
-      <c r="C528" t="inlineStr">
-        <is>
-          <t>25351673613202225</t>
-        </is>
+      <c r="C528" t="n">
+        <v>2.535167361320222e+16</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -14683,10 +13629,8 @@
           <t>carfilzomibe</t>
         </is>
       </c>
-      <c r="C529" t="inlineStr">
-        <is>
-          <t>25351255810202185</t>
-        </is>
+      <c r="C529" t="n">
+        <v>2.535125581020218e+16</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -14710,10 +13654,8 @@
           <t>trometamol cetorolaco</t>
         </is>
       </c>
-      <c r="C530" t="inlineStr">
-        <is>
-          <t>25351654225202164</t>
-        </is>
+      <c r="C530" t="n">
+        <v>2.535165422520216e+16</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -14737,10 +13679,8 @@
           <t>pitavastatina cálcica pentaidratada</t>
         </is>
       </c>
-      <c r="C531" t="inlineStr">
-        <is>
-          <t>25351527145202218</t>
-        </is>
+      <c r="C531" t="n">
+        <v>2.535152714520222e+16</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -14764,10 +13704,8 @@
           <t>besilato de levanlodipino hemipentaidratado</t>
         </is>
       </c>
-      <c r="C532" t="inlineStr">
-        <is>
-          <t>25351492777202253</t>
-        </is>
+      <c r="C532" t="n">
+        <v>2.535149277720225e+16</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -14791,10 +13729,8 @@
           <t>hidroclorotiazida</t>
         </is>
       </c>
-      <c r="C533" t="inlineStr">
-        <is>
-          <t>25351234613202211</t>
-        </is>
+      <c r="C533" t="n">
+        <v>2.535123461320221e+16</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -14818,10 +13754,8 @@
           <t>cefalexina monoidratada</t>
         </is>
       </c>
-      <c r="C534" t="inlineStr">
-        <is>
-          <t>25351196266202122</t>
-        </is>
+      <c r="C534" t="n">
+        <v>2.535119626620212e+16</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -14845,10 +13779,8 @@
           <t>aciclovir</t>
         </is>
       </c>
-      <c r="C535" t="inlineStr">
-        <is>
-          <t>25351247888202126</t>
-        </is>
+      <c r="C535" t="n">
+        <v>2.535124788820213e+16</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -14872,10 +13804,8 @@
           <t>ibuprofeno</t>
         </is>
       </c>
-      <c r="C536" t="inlineStr">
-        <is>
-          <t>25351072240202351</t>
-        </is>
+      <c r="C536" t="n">
+        <v>2.535107224020235e+16</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -14899,10 +13829,8 @@
           <t>cloridrato de metformina</t>
         </is>
       </c>
-      <c r="C537" t="inlineStr">
-        <is>
-          <t>25351583229202231</t>
-        </is>
+      <c r="C537" t="n">
+        <v>2.535158322920223e+16</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -14926,10 +13854,8 @@
           <t>cloridrato de metformina</t>
         </is>
       </c>
-      <c r="C538" t="inlineStr">
-        <is>
-          <t>25351165919202211</t>
-        </is>
+      <c r="C538" t="n">
+        <v>2.535116591920221e+16</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -14953,10 +13879,8 @@
           <t>parecoxibe sódico</t>
         </is>
       </c>
-      <c r="C539" t="inlineStr">
-        <is>
-          <t>25351000511202296</t>
-        </is>
+      <c r="C539" t="n">
+        <v>2.53510005112023e+16</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -14980,10 +13904,8 @@
           <t>fosfato de sitagliptina monoidratado</t>
         </is>
       </c>
-      <c r="C540" t="inlineStr">
-        <is>
-          <t>25351745532202153</t>
-        </is>
+      <c r="C540" t="n">
+        <v>2.535174553220215e+16</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -15007,10 +13929,8 @@
           <t>hemitartarato de zolpidem</t>
         </is>
       </c>
-      <c r="C541" t="inlineStr">
-        <is>
-          <t>25351851362202145</t>
-        </is>
+      <c r="C541" t="n">
+        <v>2.535185136220214e+16</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -15034,10 +13954,8 @@
           <t>fosfato de codeína hemi-hidratado</t>
         </is>
       </c>
-      <c r="C542" t="inlineStr">
-        <is>
-          <t>25351214747202127</t>
-        </is>
+      <c r="C542" t="n">
+        <v>2.535121474720213e+16</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -15061,10 +13979,8 @@
           <t>ocitocina</t>
         </is>
       </c>
-      <c r="C543" t="inlineStr">
-        <is>
-          <t>25351762016202193</t>
-        </is>
+      <c r="C543" t="n">
+        <v>2.535176201620219e+16</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -15088,10 +14004,8 @@
           <t>ceftriaxona dissódica hemieptaidratada</t>
         </is>
       </c>
-      <c r="C544" t="inlineStr">
-        <is>
-          <t>25351464371202108</t>
-        </is>
+      <c r="C544" t="n">
+        <v>2.535146437120211e+16</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -15115,10 +14029,8 @@
           <t>drospirenona</t>
         </is>
       </c>
-      <c r="C545" t="inlineStr">
-        <is>
-          <t>25351273206202211</t>
-        </is>
+      <c r="C545" t="n">
+        <v>2.535127320620221e+16</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -15142,10 +14054,8 @@
           <t>tazobactam</t>
         </is>
       </c>
-      <c r="C546" t="inlineStr">
-        <is>
-          <t>25351088152202291</t>
-        </is>
+      <c r="C546" t="n">
+        <v>2.535108815220229e+16</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -15169,10 +14079,8 @@
           <t>ceftriaxona dissódica hemieptaidratada</t>
         </is>
       </c>
-      <c r="C547" t="inlineStr">
-        <is>
-          <t>25351535972202102</t>
-        </is>
+      <c r="C547" t="n">
+        <v>2.53515359722021e+16</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -15196,10 +14104,8 @@
           <t>ceftazidima pentaidratada</t>
         </is>
       </c>
-      <c r="C548" t="inlineStr">
-        <is>
-          <t>25351063708202155</t>
-        </is>
+      <c r="C548" t="n">
+        <v>2.535106370820216e+16</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -15223,10 +14129,8 @@
           <t>paracetamol</t>
         </is>
       </c>
-      <c r="C549" t="inlineStr">
-        <is>
-          <t>25351898107202166</t>
-        </is>
+      <c r="C549" t="n">
+        <v>2.535189810720217e+16</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -15250,10 +14154,8 @@
           <t>etoricoxibe</t>
         </is>
       </c>
-      <c r="C550" t="inlineStr">
-        <is>
-          <t>25351514251202151</t>
-        </is>
+      <c r="C550" t="n">
+        <v>2.535151425120215e+16</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -15277,10 +14179,8 @@
           <t>brometo de rocurônio</t>
         </is>
       </c>
-      <c r="C551" t="inlineStr">
-        <is>
-          <t>25351037183202283</t>
-        </is>
+      <c r="C551" t="n">
+        <v>2.535103718320228e+16</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -15304,10 +14204,8 @@
           <t>cloridrato de doxorrubicina</t>
         </is>
       </c>
-      <c r="C552" t="inlineStr">
-        <is>
-          <t>25351604159202181</t>
-        </is>
+      <c r="C552" t="n">
+        <v>2.535160415920218e+16</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -15331,10 +14229,8 @@
           <t>cloridrato de rilpivirina</t>
         </is>
       </c>
-      <c r="C553" t="inlineStr">
-        <is>
-          <t>25351221052202100</t>
-        </is>
+      <c r="C553" t="n">
+        <v>2.53512210522021e+16</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -15358,10 +14254,8 @@
           <t>rilpivirina</t>
         </is>
       </c>
-      <c r="C554" t="inlineStr">
-        <is>
-          <t>25351381305202195</t>
-        </is>
+      <c r="C554" t="n">
+        <v>2.53513813052022e+16</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -15385,10 +14279,8 @@
           <t>etoricoxibe</t>
         </is>
       </c>
-      <c r="C555" t="inlineStr">
-        <is>
-          <t>25351459577202116</t>
-        </is>
+      <c r="C555" t="n">
+        <v>2.535145957720212e+16</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -15412,10 +14304,8 @@
           <t>piperacilina monoidratada</t>
         </is>
       </c>
-      <c r="C556" t="inlineStr">
-        <is>
-          <t>25351088151202246</t>
-        </is>
+      <c r="C556" t="n">
+        <v>2.535108815120225e+16</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -15439,10 +14329,8 @@
           <t>etinilestradiol</t>
         </is>
       </c>
-      <c r="C557" t="inlineStr">
-        <is>
-          <t>25351788882202295</t>
-        </is>
+      <c r="C557" t="n">
+        <v>2.53517888822023e+16</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -15466,10 +14354,8 @@
           <t>azitromicina di-hidratada</t>
         </is>
       </c>
-      <c r="C558" t="inlineStr">
-        <is>
-          <t>25351198490202159</t>
-        </is>
+      <c r="C558" t="n">
+        <v>2.535119849020216e+16</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -15493,10 +14379,8 @@
           <t>fampridina</t>
         </is>
       </c>
-      <c r="C559" t="inlineStr">
-        <is>
-          <t>25351007864202217</t>
-        </is>
+      <c r="C559" t="n">
+        <v>2.535100786420222e+16</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -15520,10 +14404,8 @@
           <t>bicalutamida</t>
         </is>
       </c>
-      <c r="C560" t="inlineStr">
-        <is>
-          <t>25351159727202003</t>
-        </is>
+      <c r="C560" t="n">
+        <v>2.5351159727202e+16</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -15547,10 +14429,8 @@
           <t>enzalutamida</t>
         </is>
       </c>
-      <c r="C561" t="inlineStr">
-        <is>
-          <t>25351042982202191</t>
-        </is>
+      <c r="C561" t="n">
+        <v>2.535104298220219e+16</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -15574,10 +14454,8 @@
           <t>benzilpenicilina potássica</t>
         </is>
       </c>
-      <c r="C562" t="inlineStr">
-        <is>
-          <t>25351881526202169</t>
-        </is>
+      <c r="C562" t="n">
+        <v>2.535188152620217e+16</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -15601,10 +14479,8 @@
           <t>cloridrato de doxorrubicina</t>
         </is>
       </c>
-      <c r="C563" t="inlineStr">
-        <is>
-          <t>25351666895202123</t>
-        </is>
+      <c r="C563" t="n">
+        <v>2.535166689520212e+16</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -15628,10 +14504,8 @@
           <t>carbonato de lítio</t>
         </is>
       </c>
-      <c r="C564" t="inlineStr">
-        <is>
-          <t>25351759475202190</t>
-        </is>
+      <c r="C564" t="n">
+        <v>2.535175947520219e+16</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -15655,10 +14529,8 @@
           <t>tigeciclina</t>
         </is>
       </c>
-      <c r="C565" t="inlineStr">
-        <is>
-          <t>25351970820202063</t>
-        </is>
+      <c r="C565" t="n">
+        <v>2.535197082020206e+16</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -15682,10 +14554,8 @@
           <t>succinato de desvenlafaxina monoidratado</t>
         </is>
       </c>
-      <c r="C566" t="inlineStr">
-        <is>
-          <t>25351114763202111</t>
-        </is>
+      <c r="C566" t="n">
+        <v>2.535111476320211e+16</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -15709,10 +14579,8 @@
           <t>gefitinibe</t>
         </is>
       </c>
-      <c r="C567" t="inlineStr">
-        <is>
-          <t>25351199392202139</t>
-        </is>
+      <c r="C567" t="n">
+        <v>2.535119939220214e+16</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -15736,10 +14604,8 @@
           <t>esilato de nintedanibe</t>
         </is>
       </c>
-      <c r="C568" t="inlineStr">
-        <is>
-          <t>25351382611202068</t>
-        </is>
+      <c r="C568" t="n">
+        <v>2.535138261120207e+16</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -15763,10 +14629,8 @@
           <t>cloridrato de metformina</t>
         </is>
       </c>
-      <c r="C569" t="inlineStr">
-        <is>
-          <t>25351223837202117</t>
-        </is>
+      <c r="C569" t="n">
+        <v>2.535122383720212e+16</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -15790,10 +14654,8 @@
           <t>everolimo</t>
         </is>
       </c>
-      <c r="C570" t="inlineStr">
-        <is>
-          <t>25351692063202162</t>
-        </is>
+      <c r="C570" t="n">
+        <v>2.535169206320216e+16</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -15817,10 +14679,8 @@
           <t>claritromicina</t>
         </is>
       </c>
-      <c r="C571" t="inlineStr">
-        <is>
-          <t>25351517246202281</t>
-        </is>
+      <c r="C571" t="n">
+        <v>2.535151724620228e+16</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -15844,10 +14704,8 @@
           <t>cloridrato de bendamustina monoidratada</t>
         </is>
       </c>
-      <c r="C572" t="inlineStr">
-        <is>
-          <t>25351748374202193</t>
-        </is>
+      <c r="C572" t="n">
+        <v>2.535174837420219e+16</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -15871,10 +14729,8 @@
           <t>tosilato de sorafenibe</t>
         </is>
       </c>
-      <c r="C573" t="inlineStr">
-        <is>
-          <t>25351915465202141</t>
-        </is>
+      <c r="C573" t="n">
+        <v>2.535191546520214e+16</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -15898,10 +14754,8 @@
           <t>vildagliptina</t>
         </is>
       </c>
-      <c r="C574" t="inlineStr">
-        <is>
-          <t>25351063743202255</t>
-        </is>
+      <c r="C574" t="n">
+        <v>2.535106374320226e+16</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -15925,10 +14779,8 @@
           <t>aciclovir</t>
         </is>
       </c>
-      <c r="C575" t="inlineStr">
-        <is>
-          <t>25351308050202116</t>
-        </is>
+      <c r="C575" t="n">
+        <v>2.535130805020212e+16</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -15952,10 +14804,8 @@
           <t>bussulfano</t>
         </is>
       </c>
-      <c r="C576" t="inlineStr">
-        <is>
-          <t>25351653813202181</t>
-        </is>
+      <c r="C576" t="n">
+        <v>2.535165381320218e+16</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -15979,10 +14829,8 @@
           <t>fosfato de sitagliptina</t>
         </is>
       </c>
-      <c r="C577" t="inlineStr">
-        <is>
-          <t>25351333869202031</t>
-        </is>
+      <c r="C577" t="n">
+        <v>2.535133386920203e+16</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -16006,10 +14854,8 @@
           <t>amoxicilina tri-hidratada</t>
         </is>
       </c>
-      <c r="C578" t="inlineStr">
-        <is>
-          <t>25351533263202001</t>
-        </is>
+      <c r="C578" t="n">
+        <v>2.5351533263202e+16</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -16033,10 +14879,8 @@
           <t>cloridrato de memantina</t>
         </is>
       </c>
-      <c r="C579" t="inlineStr">
-        <is>
-          <t>25351537007202166</t>
-        </is>
+      <c r="C579" t="n">
+        <v>2.535153700720217e+16</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -16060,10 +14904,8 @@
           <t>vildagliptina</t>
         </is>
       </c>
-      <c r="C580" t="inlineStr">
-        <is>
-          <t>25351871278202067</t>
-        </is>
+      <c r="C580" t="n">
+        <v>2.535187127820207e+16</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -16087,10 +14929,8 @@
           <t>rosuvastatina cálcica</t>
         </is>
       </c>
-      <c r="C581" t="inlineStr">
-        <is>
-          <t>25351322289202018</t>
-        </is>
+      <c r="C581" t="n">
+        <v>2.535132228920202e+16</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -16114,10 +14954,8 @@
           <t>cloridrato  de ondansetrona di-hidratado</t>
         </is>
       </c>
-      <c r="C582" t="inlineStr">
-        <is>
-          <t>25351163773202180</t>
-        </is>
+      <c r="C582" t="n">
+        <v>2.535116377320218e+16</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>

--- a/cadifa_completo_anterior.xlsx
+++ b/cadifa_completo_anterior.xlsx
@@ -5309,7 +5309,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>001.1</t>
+          <t>001.2</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">

--- a/cadifa_completo_anterior.xlsx
+++ b/cadifa_completo_anterior.xlsx
@@ -446,16 +446,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Bec Chemicals Private Limited</t>
+          <t>Dr Reddys Farmacêutica Do Brasil Ltda</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>cetoprofeno</t>
+          <t>gatifloxacino</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2.535118484220235e+16</v>
+        <v>2.535175579320234e+16</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -464,23 +464,23 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ami Lifesciences Private Limited</t>
+          <t>Kissei Pharmaceutical Co., Ltd.</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>tadalafila</t>
+          <t>linzagolixato de colina</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2.53512999542025e+16</v>
+        <v>2.535139970020248e+16</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -489,23 +489,23 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Kissei Pharmaceutical Co., Ltd.</t>
+          <t>Ami Lifesciences Private Limited</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>linzagolixato de colina</t>
+          <t>tadalafila</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2.535139970020248e+16</v>
+        <v>2.53512999542025e+16</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -514,23 +514,23 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ipca Laboratories Ltd.</t>
+          <t>Heraeus Deutschland Gmbh &amp; Co. Kg</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hidroclorotiazida</t>
+          <t>cloridrato do ácido aminolevulínico</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2.53512272772026e+16</v>
+        <v>2.53511450242025e+16</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -539,23 +539,23 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Honour Lab Limited</t>
+          <t>Zydus Lifesciences Limited</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>brexpiprazol</t>
+          <t>bromidrato de vortioxetina</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2.53510759682025e+16</v>
+        <v>2.535114187120259e+16</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -564,23 +564,23 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Heraeus Deutschland Gmbh &amp; Co. Kg</t>
+          <t>Bec Chemicals Private Limited</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>cloridrato do ácido aminolevulínico</t>
+          <t>cetoprofeno</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2.53511450242025e+16</v>
+        <v>2.535118484220235e+16</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -589,23 +589,23 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Alivus Life Sciences Limited</t>
+          <t>Changzhou Pharmaceutical Factory</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>dicloridrato de levocetirizina</t>
+          <t>lenalidomida</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2.535137267820226e+16</v>
+        <v>2.535156734920237e+16</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
     </row>
@@ -639,23 +639,23 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Changzhou Pharmaceutical Factory</t>
+          <t>Alivus Life Sciences Limited</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>lenalidomida</t>
+          <t>dicloridrato de levocetirizina</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2.535156734920237e+16</v>
+        <v>2.535137267820226e+16</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -664,23 +664,23 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ranke Química S.A.</t>
+          <t>Ipca Laboratories Ltd.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ebastina</t>
+          <t>hidroclorotiazida</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2.535157027720226e+16</v>
+        <v>2.53512272772026e+16</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -689,23 +689,23 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Dr Reddys Farmacêutica Do Brasil Ltda</t>
+          <t>Ranke Química S.A.</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>levofloxacino hemi-hidratado</t>
+          <t>ebastina</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2.535195780920243e+16</v>
+        <v>2.535157027720226e+16</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -714,23 +714,23 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Msn Laboratories Private Limited</t>
+          <t>Honour Lab Limited</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>carfilzomibe</t>
+          <t>ticagrelor</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2.53515140992023e+16</v>
+        <v>2.535115692720252e+16</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -739,23 +739,23 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Shandong Anshun Pharmaceutical Co., Ltd.</t>
+          <t>Honour Lab Limited</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>piperacilina monoidratada</t>
+          <t>brexpiprazol</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2.53513876412025e+16</v>
+        <v>2.53510759682025e+16</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
     </row>
@@ -776,11 +776,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>gatifloxacino</t>
+          <t>levofloxacino hemi-hidratado</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2.535175579320234e+16</v>
+        <v>2.535195780920243e+16</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -796,16 +796,16 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Honour Lab Limited</t>
+          <t>Msn Laboratories Private Limited</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ticagrelor</t>
+          <t>carfilzomibe</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2.535115692720252e+16</v>
+        <v>2.53515140992023e+16</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -821,16 +821,16 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Alivus Life Sciences Limited</t>
+          <t>Shandong Anshun Pharmaceutical Co., Ltd.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>cloridrato de lurasidona</t>
+          <t>piperacilina monoidratada</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2.535122114620241e+16</v>
+        <v>2.53513876412025e+16</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -846,16 +846,16 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Malladi Drugs &amp; Pharmaceuticals Limited</t>
+          <t>Alivus Life Sciences Limited</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>cloridrato de pseudoefedrina</t>
+          <t>cloridrato de lurasidona</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2.535119730420233e+16</v>
+        <v>2.535122114620241e+16</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -871,16 +871,16 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Zhuhai Rundu Pharmaceutical Co., Ltd.</t>
+          <t>Malladi Drugs &amp; Pharmaceuticals Limited</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>sacubitril valsartana sódica hidratada</t>
+          <t>cloridrato de pseudoefedrina</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2.535138675820245e+16</v>
+        <v>2.535119730420233e+16</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Zaklady Farmaceutyczne Polpharma S.A.</t>
+          <t>Zhuhai Rundu Pharmaceutical Co., Ltd.</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ibandronato de sódio monoidratado</t>
+          <t>sacubitril valsartana sódica hidratada</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2.535115404120228e+16</v>
+        <v>2.535138675820245e+16</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -921,16 +921,16 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Hubei Biocause Heilen Pharmaceutical Co., Ltd</t>
+          <t>Zaklady Farmaceutyczne Polpharma S.A.</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>dexibuprofeno</t>
+          <t>ibandronato de sódio monoidratado</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2.535113803620249e+16</v>
+        <v>2.535115404120228e+16</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -946,16 +946,16 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Hetero Labs Limited</t>
+          <t>Hubei Biocause Heilen Pharmaceutical Co., Ltd</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>enzalutamida</t>
+          <t>dexibuprofeno</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2.535103161420254e+16</v>
+        <v>2.535113803620249e+16</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -971,16 +971,16 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Zhejiang Huahai Pharmaceutical Co., Ltd.</t>
+          <t>Hetero Labs Limited</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>linagliptina</t>
+          <t>enzalutamida</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2.535151748720232e+16</v>
+        <v>2.535103161420254e+16</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
     </row>
@@ -1001,11 +1001,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>olmesartana medoxomila</t>
+          <t>linagliptina</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2.535145427120242e+16</v>
+        <v>2.535151748720232e+16</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1021,16 +1021,16 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Dr Reddys Farmacêutica Do Brasil Ltda</t>
+          <t>Zhejiang Huahai Pharmaceutical Co., Ltd.</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>naproxeno sódico</t>
+          <t>olmesartana medoxomila</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2.53514056232024e+16</v>
+        <v>2.535145427120242e+16</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1046,16 +1046,16 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Honour Lab Limited</t>
+          <t>Dr Reddys Farmacêutica Do Brasil Ltda</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>cloridrato de fingolimode</t>
+          <t>naproxeno sódico</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2.535165000320225e+16</v>
+        <v>2.53514056232024e+16</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1071,16 +1071,16 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Zydus Lifesciences Limited</t>
+          <t>Honour Lab Limited</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>bromidrato de vortioxetina</t>
+          <t>cloridrato de fingolimode</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2.535114187120259e+16</v>
+        <v>2.535165000320225e+16</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
     </row>

--- a/cadifa_completo_anterior.xlsx
+++ b/cadifa_completo_anterior.xlsx
@@ -7059,7 +7059,7 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>002</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -7334,7 +7334,7 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>002</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -9659,7 +9659,7 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>002</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
@@ -11284,7 +11284,7 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>002</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
@@ -12134,7 +12134,7 @@
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>002</t>
         </is>
       </c>
       <c r="E469" t="inlineStr">
@@ -12734,7 +12734,7 @@
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>002</t>
         </is>
       </c>
       <c r="E493" t="inlineStr">
@@ -13084,7 +13084,7 @@
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>003</t>
         </is>
       </c>
       <c r="E507" t="inlineStr">
@@ -14459,7 +14459,7 @@
       </c>
       <c r="D562" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>002</t>
         </is>
       </c>
       <c r="E562" t="inlineStr">
@@ -15359,7 +15359,7 @@
       </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>002</t>
         </is>
       </c>
       <c r="E598" t="inlineStr">
@@ -15384,7 +15384,7 @@
       </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>002</t>
         </is>
       </c>
       <c r="E599" t="inlineStr">
@@ -15509,7 +15509,7 @@
       </c>
       <c r="D604" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>002</t>
         </is>
       </c>
       <c r="E604" t="inlineStr">
@@ -15709,7 +15709,7 @@
       </c>
       <c r="D612" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>002</t>
         </is>
       </c>
       <c r="E612" t="inlineStr">
